--- a/exp1/experiment_results.xlsx
+++ b/exp1/experiment_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DZ325"/>
+  <dimension ref="A1:EA329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1079,6 +1079,11 @@
           <t>DGD_RMSE</t>
         </is>
       </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>dgd_lr</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1131,7 +1136,7 @@
       <c r="N2" t="n">
         <v>95</v>
       </c>
-      <c r="O2" t="b">
+      <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
@@ -1313,6 +1318,7 @@
       <c r="DX2" t="inlineStr"/>
       <c r="DY2" t="inlineStr"/>
       <c r="DZ2" t="inlineStr"/>
+      <c r="EA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1365,7 +1371,7 @@
       <c r="N3" t="n">
         <v>95</v>
       </c>
-      <c r="O3" t="b">
+      <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
@@ -1547,6 +1553,7 @@
       <c r="DX3" t="inlineStr"/>
       <c r="DY3" t="inlineStr"/>
       <c r="DZ3" t="inlineStr"/>
+      <c r="EA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1600,7 +1607,7 @@
       <c r="N4" t="n">
         <v>95</v>
       </c>
-      <c r="O4" t="b">
+      <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
@@ -1782,6 +1789,7 @@
       <c r="DX4" t="inlineStr"/>
       <c r="DY4" t="inlineStr"/>
       <c r="DZ4" t="inlineStr"/>
+      <c r="EA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1834,7 +1842,7 @@
       <c r="N5" t="n">
         <v>95</v>
       </c>
-      <c r="O5" t="b">
+      <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
@@ -2016,6 +2024,7 @@
       <c r="DX5" t="inlineStr"/>
       <c r="DY5" t="inlineStr"/>
       <c r="DZ5" t="inlineStr"/>
+      <c r="EA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2068,7 +2077,7 @@
       <c r="N6" t="n">
         <v>95</v>
       </c>
-      <c r="O6" t="b">
+      <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
@@ -2250,6 +2259,7 @@
       <c r="DX6" t="inlineStr"/>
       <c r="DY6" t="inlineStr"/>
       <c r="DZ6" t="inlineStr"/>
+      <c r="EA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2303,7 +2313,7 @@
       <c r="N7" t="n">
         <v>95</v>
       </c>
-      <c r="O7" t="b">
+      <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
@@ -2485,6 +2495,7 @@
       <c r="DX7" t="inlineStr"/>
       <c r="DY7" t="inlineStr"/>
       <c r="DZ7" t="inlineStr"/>
+      <c r="EA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2537,7 +2548,7 @@
       <c r="N8" t="n">
         <v>95</v>
       </c>
-      <c r="O8" t="b">
+      <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
@@ -2719,6 +2730,7 @@
       <c r="DX8" t="inlineStr"/>
       <c r="DY8" t="inlineStr"/>
       <c r="DZ8" t="inlineStr"/>
+      <c r="EA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2772,7 +2784,7 @@
       <c r="N9" t="n">
         <v>95</v>
       </c>
-      <c r="O9" t="b">
+      <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
@@ -2954,6 +2966,7 @@
       <c r="DX9" t="inlineStr"/>
       <c r="DY9" t="inlineStr"/>
       <c r="DZ9" t="inlineStr"/>
+      <c r="EA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3007,7 +3020,7 @@
       <c r="N10" t="n">
         <v>95</v>
       </c>
-      <c r="O10" t="b">
+      <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
@@ -3189,6 +3202,7 @@
       <c r="DX10" t="inlineStr"/>
       <c r="DY10" t="inlineStr"/>
       <c r="DZ10" t="inlineStr"/>
+      <c r="EA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3242,7 +3256,7 @@
       <c r="N11" t="n">
         <v>95</v>
       </c>
-      <c r="O11" t="b">
+      <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
@@ -3424,6 +3438,7 @@
       <c r="DX11" t="inlineStr"/>
       <c r="DY11" t="inlineStr"/>
       <c r="DZ11" t="inlineStr"/>
+      <c r="EA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3477,7 +3492,7 @@
       <c r="N12" t="n">
         <v>95</v>
       </c>
-      <c r="O12" t="b">
+      <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
@@ -3659,6 +3674,7 @@
       <c r="DX12" t="inlineStr"/>
       <c r="DY12" t="inlineStr"/>
       <c r="DZ12" t="inlineStr"/>
+      <c r="EA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3712,7 +3728,7 @@
       <c r="N13" t="n">
         <v>95</v>
       </c>
-      <c r="O13" t="b">
+      <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
@@ -3894,6 +3910,7 @@
       <c r="DX13" t="inlineStr"/>
       <c r="DY13" t="inlineStr"/>
       <c r="DZ13" t="inlineStr"/>
+      <c r="EA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3947,7 +3964,7 @@
       <c r="N14" t="n">
         <v>95</v>
       </c>
-      <c r="O14" t="b">
+      <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
@@ -4129,6 +4146,7 @@
       <c r="DX14" t="inlineStr"/>
       <c r="DY14" t="inlineStr"/>
       <c r="DZ14" t="inlineStr"/>
+      <c r="EA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4182,7 +4200,7 @@
       <c r="N15" t="n">
         <v>95</v>
       </c>
-      <c r="O15" t="b">
+      <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
@@ -4364,6 +4382,7 @@
       <c r="DX15" t="inlineStr"/>
       <c r="DY15" t="inlineStr"/>
       <c r="DZ15" t="inlineStr"/>
+      <c r="EA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4417,7 +4436,7 @@
       <c r="N16" t="n">
         <v>95</v>
       </c>
-      <c r="O16" t="b">
+      <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
@@ -4599,6 +4618,7 @@
       <c r="DX16" t="inlineStr"/>
       <c r="DY16" t="inlineStr"/>
       <c r="DZ16" t="inlineStr"/>
+      <c r="EA16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4652,7 +4672,7 @@
       <c r="N17" t="n">
         <v>295</v>
       </c>
-      <c r="O17" t="b">
+      <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
@@ -4834,6 +4854,7 @@
       <c r="DX17" t="inlineStr"/>
       <c r="DY17" t="inlineStr"/>
       <c r="DZ17" t="inlineStr"/>
+      <c r="EA17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4887,7 +4908,7 @@
       <c r="N18" t="n">
         <v>295</v>
       </c>
-      <c r="O18" t="b">
+      <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
@@ -5069,6 +5090,7 @@
       <c r="DX18" t="inlineStr"/>
       <c r="DY18" t="inlineStr"/>
       <c r="DZ18" t="inlineStr"/>
+      <c r="EA18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5122,7 +5144,7 @@
       <c r="N19" t="n">
         <v>25</v>
       </c>
-      <c r="O19" t="b">
+      <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
@@ -5304,6 +5326,7 @@
       <c r="DX19" t="inlineStr"/>
       <c r="DY19" t="inlineStr"/>
       <c r="DZ19" t="inlineStr"/>
+      <c r="EA19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5357,7 +5380,7 @@
       <c r="N20" t="n">
         <v>25</v>
       </c>
-      <c r="O20" t="b">
+      <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
@@ -5539,6 +5562,7 @@
       <c r="DX20" t="inlineStr"/>
       <c r="DY20" t="inlineStr"/>
       <c r="DZ20" t="inlineStr"/>
+      <c r="EA20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5592,7 +5616,7 @@
       <c r="N21" t="n">
         <v>25</v>
       </c>
-      <c r="O21" t="b">
+      <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
@@ -5774,6 +5798,7 @@
       <c r="DX21" t="inlineStr"/>
       <c r="DY21" t="inlineStr"/>
       <c r="DZ21" t="inlineStr"/>
+      <c r="EA21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5827,7 +5852,7 @@
       <c r="N22" t="n">
         <v>425</v>
       </c>
-      <c r="O22" t="b">
+      <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
@@ -6009,6 +6034,7 @@
       <c r="DX22" t="inlineStr"/>
       <c r="DY22" t="inlineStr"/>
       <c r="DZ22" t="inlineStr"/>
+      <c r="EA22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6062,7 +6088,7 @@
       <c r="N23" t="n">
         <v>425</v>
       </c>
-      <c r="O23" t="b">
+      <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
@@ -6244,6 +6270,7 @@
       <c r="DX23" t="inlineStr"/>
       <c r="DY23" t="inlineStr"/>
       <c r="DZ23" t="inlineStr"/>
+      <c r="EA23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6297,7 +6324,7 @@
       <c r="N24" t="n">
         <v>425</v>
       </c>
-      <c r="O24" t="b">
+      <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
@@ -6479,6 +6506,7 @@
       <c r="DX24" t="inlineStr"/>
       <c r="DY24" t="inlineStr"/>
       <c r="DZ24" t="inlineStr"/>
+      <c r="EA24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6532,7 +6560,7 @@
       <c r="N25" t="n">
         <v>425</v>
       </c>
-      <c r="O25" t="b">
+      <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
@@ -6714,6 +6742,7 @@
       <c r="DX25" t="inlineStr"/>
       <c r="DY25" t="inlineStr"/>
       <c r="DZ25" t="inlineStr"/>
+      <c r="EA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6767,7 +6796,7 @@
       <c r="N26" t="n">
         <v>425</v>
       </c>
-      <c r="O26" t="b">
+      <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
@@ -6949,6 +6978,7 @@
       <c r="DX26" t="inlineStr"/>
       <c r="DY26" t="inlineStr"/>
       <c r="DZ26" t="inlineStr"/>
+      <c r="EA26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7002,7 +7032,7 @@
       <c r="N27" t="n">
         <v>425</v>
       </c>
-      <c r="O27" t="b">
+      <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
@@ -7184,6 +7214,7 @@
       <c r="DX27" t="inlineStr"/>
       <c r="DY27" t="inlineStr"/>
       <c r="DZ27" t="inlineStr"/>
+      <c r="EA27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7237,7 +7268,7 @@
       <c r="N28" t="n">
         <v>415</v>
       </c>
-      <c r="O28" t="b">
+      <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
@@ -7419,6 +7450,7 @@
       <c r="DX28" t="inlineStr"/>
       <c r="DY28" t="inlineStr"/>
       <c r="DZ28" t="inlineStr"/>
+      <c r="EA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7472,7 +7504,7 @@
       <c r="N29" t="n">
         <v>415</v>
       </c>
-      <c r="O29" t="b">
+      <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
@@ -7654,6 +7686,7 @@
       <c r="DX29" t="inlineStr"/>
       <c r="DY29" t="inlineStr"/>
       <c r="DZ29" t="inlineStr"/>
+      <c r="EA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7707,7 +7740,7 @@
       <c r="N30" t="n">
         <v>415</v>
       </c>
-      <c r="O30" t="b">
+      <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
@@ -7889,6 +7922,7 @@
       <c r="DX30" t="inlineStr"/>
       <c r="DY30" t="inlineStr"/>
       <c r="DZ30" t="inlineStr"/>
+      <c r="EA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7942,7 +7976,7 @@
       <c r="N31" t="n">
         <v>465</v>
       </c>
-      <c r="O31" t="b">
+      <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
@@ -8124,6 +8158,7 @@
       <c r="DX31" t="inlineStr"/>
       <c r="DY31" t="inlineStr"/>
       <c r="DZ31" t="inlineStr"/>
+      <c r="EA31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8177,7 +8212,7 @@
       <c r="N32" t="n">
         <v>465</v>
       </c>
-      <c r="O32" t="b">
+      <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
@@ -8359,6 +8394,7 @@
       <c r="DX32" t="inlineStr"/>
       <c r="DY32" t="inlineStr"/>
       <c r="DZ32" t="inlineStr"/>
+      <c r="EA32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8412,7 +8448,7 @@
       <c r="N33" t="n">
         <v>465</v>
       </c>
-      <c r="O33" t="b">
+      <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
@@ -8594,6 +8630,7 @@
       <c r="DX33" t="inlineStr"/>
       <c r="DY33" t="inlineStr"/>
       <c r="DZ33" t="inlineStr"/>
+      <c r="EA33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8649,7 +8686,7 @@
       <c r="N34" t="n">
         <v>465</v>
       </c>
-      <c r="O34" t="b">
+      <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
@@ -8831,6 +8868,7 @@
       <c r="DX34" t="inlineStr"/>
       <c r="DY34" t="inlineStr"/>
       <c r="DZ34" t="inlineStr"/>
+      <c r="EA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8884,7 +8922,7 @@
       <c r="N35" t="n">
         <v>45</v>
       </c>
-      <c r="O35" t="b">
+      <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
@@ -9066,6 +9104,7 @@
       <c r="DX35" t="inlineStr"/>
       <c r="DY35" t="inlineStr"/>
       <c r="DZ35" t="inlineStr"/>
+      <c r="EA35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9119,7 +9158,7 @@
       <c r="N36" t="n">
         <v>45</v>
       </c>
-      <c r="O36" t="b">
+      <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
@@ -9301,6 +9340,7 @@
       <c r="DX36" t="inlineStr"/>
       <c r="DY36" t="inlineStr"/>
       <c r="DZ36" t="inlineStr"/>
+      <c r="EA36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -9354,7 +9394,7 @@
       <c r="N37" t="n">
         <v>45</v>
       </c>
-      <c r="O37" t="b">
+      <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
@@ -9536,6 +9576,7 @@
       <c r="DX37" t="inlineStr"/>
       <c r="DY37" t="inlineStr"/>
       <c r="DZ37" t="inlineStr"/>
+      <c r="EA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -9589,7 +9630,7 @@
       <c r="N38" t="n">
         <v>45</v>
       </c>
-      <c r="O38" t="b">
+      <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
@@ -9771,6 +9812,7 @@
       <c r="DX38" t="inlineStr"/>
       <c r="DY38" t="inlineStr"/>
       <c r="DZ38" t="inlineStr"/>
+      <c r="EA38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9824,7 +9866,7 @@
       <c r="N39" t="n">
         <v>45</v>
       </c>
-      <c r="O39" t="b">
+      <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
@@ -10006,6 +10048,7 @@
       <c r="DX39" t="inlineStr"/>
       <c r="DY39" t="inlineStr"/>
       <c r="DZ39" t="inlineStr"/>
+      <c r="EA39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -10059,7 +10102,7 @@
       <c r="N40" t="n">
         <v>45</v>
       </c>
-      <c r="O40" t="b">
+      <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
@@ -10241,6 +10284,7 @@
       <c r="DX40" t="inlineStr"/>
       <c r="DY40" t="inlineStr"/>
       <c r="DZ40" t="inlineStr"/>
+      <c r="EA40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -10294,7 +10338,7 @@
       <c r="N41" t="n">
         <v>45</v>
       </c>
-      <c r="O41" t="b">
+      <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
@@ -10476,6 +10520,7 @@
       <c r="DX41" t="inlineStr"/>
       <c r="DY41" t="inlineStr"/>
       <c r="DZ41" t="inlineStr"/>
+      <c r="EA41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -10529,7 +10574,7 @@
       <c r="N42" t="n">
         <v>45</v>
       </c>
-      <c r="O42" t="b">
+      <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
@@ -10711,6 +10756,7 @@
       <c r="DX42" t="inlineStr"/>
       <c r="DY42" t="inlineStr"/>
       <c r="DZ42" t="inlineStr"/>
+      <c r="EA42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -10764,7 +10810,7 @@
       <c r="N43" t="n">
         <v>45</v>
       </c>
-      <c r="O43" t="b">
+      <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
@@ -10946,6 +10992,7 @@
       <c r="DX43" t="inlineStr"/>
       <c r="DY43" t="inlineStr"/>
       <c r="DZ43" t="inlineStr"/>
+      <c r="EA43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -10999,7 +11046,7 @@
       <c r="N44" t="n">
         <v>45</v>
       </c>
-      <c r="O44" t="b">
+      <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
@@ -11181,6 +11228,7 @@
       <c r="DX44" t="inlineStr"/>
       <c r="DY44" t="inlineStr"/>
       <c r="DZ44" t="inlineStr"/>
+      <c r="EA44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -11234,7 +11282,7 @@
       <c r="N45" t="n">
         <v>45</v>
       </c>
-      <c r="O45" t="b">
+      <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
@@ -11416,6 +11464,7 @@
       <c r="DX45" t="inlineStr"/>
       <c r="DY45" t="inlineStr"/>
       <c r="DZ45" t="inlineStr"/>
+      <c r="EA45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -11469,7 +11518,7 @@
       <c r="N46" t="n">
         <v>45</v>
       </c>
-      <c r="O46" t="b">
+      <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
@@ -11651,6 +11700,7 @@
       <c r="DX46" t="inlineStr"/>
       <c r="DY46" t="inlineStr"/>
       <c r="DZ46" t="inlineStr"/>
+      <c r="EA46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -11704,7 +11754,7 @@
       <c r="N47" t="n">
         <v>45</v>
       </c>
-      <c r="O47" t="b">
+      <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
@@ -11886,6 +11936,7 @@
       <c r="DX47" t="inlineStr"/>
       <c r="DY47" t="inlineStr"/>
       <c r="DZ47" t="inlineStr"/>
+      <c r="EA47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -11939,7 +11990,7 @@
       <c r="N48" t="n">
         <v>45</v>
       </c>
-      <c r="O48" t="b">
+      <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
@@ -12121,6 +12172,7 @@
       <c r="DX48" t="inlineStr"/>
       <c r="DY48" t="inlineStr"/>
       <c r="DZ48" t="inlineStr"/>
+      <c r="EA48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -12174,7 +12226,7 @@
       <c r="N49" t="n">
         <v>145</v>
       </c>
-      <c r="O49" t="b">
+      <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
@@ -12356,6 +12408,7 @@
       <c r="DX49" t="inlineStr"/>
       <c r="DY49" t="inlineStr"/>
       <c r="DZ49" t="inlineStr"/>
+      <c r="EA49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -12409,7 +12462,7 @@
       <c r="N50" t="n">
         <v>95</v>
       </c>
-      <c r="O50" t="b">
+      <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
@@ -12591,6 +12644,7 @@
       <c r="DX50" t="inlineStr"/>
       <c r="DY50" t="inlineStr"/>
       <c r="DZ50" t="inlineStr"/>
+      <c r="EA50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -12644,7 +12698,7 @@
       <c r="N51" t="n">
         <v>145</v>
       </c>
-      <c r="O51" t="b">
+      <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
@@ -12826,6 +12880,7 @@
       <c r="DX51" t="inlineStr"/>
       <c r="DY51" t="inlineStr"/>
       <c r="DZ51" t="inlineStr"/>
+      <c r="EA51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -12877,7 +12932,7 @@
       <c r="N52" t="n">
         <v>95</v>
       </c>
-      <c r="O52" t="b">
+      <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
@@ -13059,6 +13114,7 @@
       <c r="DX52" t="inlineStr"/>
       <c r="DY52" t="inlineStr"/>
       <c r="DZ52" t="inlineStr"/>
+      <c r="EA52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -13110,7 +13166,7 @@
       <c r="N53" t="n">
         <v>145</v>
       </c>
-      <c r="O53" t="b">
+      <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
@@ -13292,6 +13348,7 @@
       <c r="DX53" t="inlineStr"/>
       <c r="DY53" t="inlineStr"/>
       <c r="DZ53" t="inlineStr"/>
+      <c r="EA53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -13343,7 +13400,7 @@
       <c r="N54" t="n">
         <v>245</v>
       </c>
-      <c r="O54" t="b">
+      <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
@@ -13525,6 +13582,7 @@
       <c r="DX54" t="inlineStr"/>
       <c r="DY54" t="inlineStr"/>
       <c r="DZ54" t="inlineStr"/>
+      <c r="EA54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -13576,7 +13634,7 @@
       <c r="N55" t="n">
         <v>245</v>
       </c>
-      <c r="O55" t="b">
+      <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
@@ -13758,6 +13816,7 @@
       <c r="DX55" t="inlineStr"/>
       <c r="DY55" t="inlineStr"/>
       <c r="DZ55" t="inlineStr"/>
+      <c r="EA55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -13808,7 +13867,7 @@
       <c r="N56" t="n">
         <v>245</v>
       </c>
-      <c r="O56" t="b">
+      <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
@@ -13990,6 +14049,7 @@
       <c r="DX56" t="inlineStr"/>
       <c r="DY56" t="inlineStr"/>
       <c r="DZ56" t="inlineStr"/>
+      <c r="EA56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -14040,7 +14100,7 @@
       <c r="N57" t="n">
         <v>245</v>
       </c>
-      <c r="O57" t="b">
+      <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
@@ -14222,6 +14282,7 @@
       <c r="DX57" t="inlineStr"/>
       <c r="DY57" t="inlineStr"/>
       <c r="DZ57" t="inlineStr"/>
+      <c r="EA57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -14274,7 +14335,7 @@
       <c r="N58" t="n">
         <v>95</v>
       </c>
-      <c r="O58" t="b">
+      <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
@@ -14456,6 +14517,7 @@
       <c r="DX58" t="inlineStr"/>
       <c r="DY58" t="inlineStr"/>
       <c r="DZ58" t="inlineStr"/>
+      <c r="EA58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -14508,7 +14570,7 @@
       <c r="N59" t="n">
         <v>95</v>
       </c>
-      <c r="O59" t="b">
+      <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
@@ -14690,6 +14752,7 @@
       <c r="DX59" t="inlineStr"/>
       <c r="DY59" t="inlineStr"/>
       <c r="DZ59" t="inlineStr"/>
+      <c r="EA59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -14740,7 +14803,7 @@
       <c r="N60" t="n">
         <v>245</v>
       </c>
-      <c r="O60" t="b">
+      <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
@@ -14922,6 +14985,7 @@
       <c r="DX60" t="inlineStr"/>
       <c r="DY60" t="inlineStr"/>
       <c r="DZ60" t="inlineStr"/>
+      <c r="EA60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -14972,7 +15036,7 @@
       <c r="N61" t="n">
         <v>245</v>
       </c>
-      <c r="O61" t="b">
+      <c r="O61" t="n">
         <v>0</v>
       </c>
       <c r="P61" t="n">
@@ -15154,6 +15218,7 @@
       <c r="DX61" t="inlineStr"/>
       <c r="DY61" t="inlineStr"/>
       <c r="DZ61" t="inlineStr"/>
+      <c r="EA61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -15204,7 +15269,7 @@
       <c r="N62" t="n">
         <v>245</v>
       </c>
-      <c r="O62" t="b">
+      <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
@@ -15386,6 +15451,7 @@
       <c r="DX62" t="inlineStr"/>
       <c r="DY62" t="inlineStr"/>
       <c r="DZ62" t="inlineStr"/>
+      <c r="EA62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -15436,7 +15502,7 @@
       <c r="N63" t="n">
         <v>245</v>
       </c>
-      <c r="O63" t="b">
+      <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
@@ -15618,6 +15684,7 @@
       <c r="DX63" t="inlineStr"/>
       <c r="DY63" t="inlineStr"/>
       <c r="DZ63" t="inlineStr"/>
+      <c r="EA63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -15668,7 +15735,7 @@
       <c r="N64" t="n">
         <v>245</v>
       </c>
-      <c r="O64" t="b">
+      <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
@@ -15850,6 +15917,7 @@
       <c r="DX64" t="inlineStr"/>
       <c r="DY64" t="inlineStr"/>
       <c r="DZ64" t="inlineStr"/>
+      <c r="EA64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -15900,7 +15968,7 @@
       <c r="N65" t="n">
         <v>245</v>
       </c>
-      <c r="O65" t="b">
+      <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
@@ -16082,6 +16150,7 @@
       <c r="DX65" t="inlineStr"/>
       <c r="DY65" t="inlineStr"/>
       <c r="DZ65" t="inlineStr"/>
+      <c r="EA65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -16132,7 +16201,7 @@
       <c r="N66" t="n">
         <v>245</v>
       </c>
-      <c r="O66" t="b">
+      <c r="O66" t="n">
         <v>0</v>
       </c>
       <c r="P66" t="n">
@@ -16314,6 +16383,7 @@
       <c r="DX66" t="inlineStr"/>
       <c r="DY66" t="inlineStr"/>
       <c r="DZ66" t="inlineStr"/>
+      <c r="EA66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -16364,7 +16434,7 @@
       <c r="N67" t="n">
         <v>25</v>
       </c>
-      <c r="O67" t="b">
+      <c r="O67" t="n">
         <v>0</v>
       </c>
       <c r="P67" t="n">
@@ -16546,6 +16616,7 @@
       <c r="DX67" t="inlineStr"/>
       <c r="DY67" t="inlineStr"/>
       <c r="DZ67" t="inlineStr"/>
+      <c r="EA67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -16598,7 +16669,7 @@
       <c r="N68" t="n">
         <v>95</v>
       </c>
-      <c r="O68" t="b">
+      <c r="O68" t="n">
         <v>0</v>
       </c>
       <c r="P68" t="n">
@@ -16780,6 +16851,7 @@
       <c r="DX68" t="inlineStr"/>
       <c r="DY68" t="inlineStr"/>
       <c r="DZ68" t="inlineStr"/>
+      <c r="EA68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -16832,7 +16904,7 @@
       <c r="N69" t="n">
         <v>95</v>
       </c>
-      <c r="O69" t="b">
+      <c r="O69" t="n">
         <v>0</v>
       </c>
       <c r="P69" t="n">
@@ -17014,6 +17086,7 @@
       <c r="DX69" t="inlineStr"/>
       <c r="DY69" t="inlineStr"/>
       <c r="DZ69" t="inlineStr"/>
+      <c r="EA69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -17066,7 +17139,7 @@
       <c r="N70" t="n">
         <v>495</v>
       </c>
-      <c r="O70" t="b">
+      <c r="O70" t="n">
         <v>0</v>
       </c>
       <c r="P70" t="n">
@@ -17248,6 +17321,7 @@
       <c r="DX70" t="inlineStr"/>
       <c r="DY70" t="inlineStr"/>
       <c r="DZ70" t="inlineStr"/>
+      <c r="EA70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -17300,7 +17374,7 @@
       <c r="N71" t="n">
         <v>85</v>
       </c>
-      <c r="O71" t="b">
+      <c r="O71" t="n">
         <v>0</v>
       </c>
       <c r="P71" t="n">
@@ -17482,6 +17556,7 @@
       <c r="DX71" t="inlineStr"/>
       <c r="DY71" t="inlineStr"/>
       <c r="DZ71" t="inlineStr"/>
+      <c r="EA71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -17534,7 +17609,7 @@
       <c r="N72" t="n">
         <v>85</v>
       </c>
-      <c r="O72" t="b">
+      <c r="O72" t="n">
         <v>0</v>
       </c>
       <c r="P72" t="n">
@@ -17716,6 +17791,7 @@
       <c r="DX72" t="inlineStr"/>
       <c r="DY72" t="inlineStr"/>
       <c r="DZ72" t="inlineStr"/>
+      <c r="EA72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -17769,7 +17845,7 @@
       <c r="N73" t="n">
         <v>85</v>
       </c>
-      <c r="O73" t="b">
+      <c r="O73" t="n">
         <v>0</v>
       </c>
       <c r="P73" t="n">
@@ -17951,6 +18027,7 @@
       <c r="DX73" t="inlineStr"/>
       <c r="DY73" t="inlineStr"/>
       <c r="DZ73" t="inlineStr"/>
+      <c r="EA73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -18004,7 +18081,7 @@
       <c r="N74" t="n">
         <v>85</v>
       </c>
-      <c r="O74" t="b">
+      <c r="O74" t="n">
         <v>0</v>
       </c>
       <c r="P74" t="n">
@@ -18186,6 +18263,7 @@
       <c r="DX74" t="inlineStr"/>
       <c r="DY74" t="inlineStr"/>
       <c r="DZ74" t="inlineStr"/>
+      <c r="EA74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -18239,7 +18317,7 @@
       <c r="N75" t="n">
         <v>85</v>
       </c>
-      <c r="O75" t="b">
+      <c r="O75" t="n">
         <v>0</v>
       </c>
       <c r="P75" t="n">
@@ -18421,6 +18499,7 @@
       <c r="DX75" t="inlineStr"/>
       <c r="DY75" t="inlineStr"/>
       <c r="DZ75" t="inlineStr"/>
+      <c r="EA75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -18474,7 +18553,7 @@
       <c r="N76" t="n">
         <v>85</v>
       </c>
-      <c r="O76" t="b">
+      <c r="O76" t="n">
         <v>0</v>
       </c>
       <c r="P76" t="n">
@@ -18656,6 +18735,7 @@
       <c r="DX76" t="inlineStr"/>
       <c r="DY76" t="inlineStr"/>
       <c r="DZ76" t="inlineStr"/>
+      <c r="EA76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -18709,7 +18789,7 @@
       <c r="N77" t="n">
         <v>185</v>
       </c>
-      <c r="O77" t="b">
+      <c r="O77" t="n">
         <v>0</v>
       </c>
       <c r="P77" t="n">
@@ -18891,6 +18971,7 @@
       <c r="DX77" t="inlineStr"/>
       <c r="DY77" t="inlineStr"/>
       <c r="DZ77" t="inlineStr"/>
+      <c r="EA77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -18944,7 +19025,7 @@
       <c r="N78" t="n">
         <v>785</v>
       </c>
-      <c r="O78" t="b">
+      <c r="O78" t="n">
         <v>0</v>
       </c>
       <c r="P78" t="n">
@@ -19126,6 +19207,7 @@
       <c r="DX78" t="inlineStr"/>
       <c r="DY78" t="inlineStr"/>
       <c r="DZ78" t="inlineStr"/>
+      <c r="EA78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -19179,7 +19261,7 @@
       <c r="N79" t="n">
         <v>785</v>
       </c>
-      <c r="O79" t="b">
+      <c r="O79" t="n">
         <v>0</v>
       </c>
       <c r="P79" t="n">
@@ -19361,6 +19443,7 @@
       <c r="DX79" t="inlineStr"/>
       <c r="DY79" t="inlineStr"/>
       <c r="DZ79" t="inlineStr"/>
+      <c r="EA79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -19414,7 +19497,7 @@
       <c r="N80" t="n">
         <v>785</v>
       </c>
-      <c r="O80" t="b">
+      <c r="O80" t="n">
         <v>0</v>
       </c>
       <c r="P80" t="n">
@@ -19596,6 +19679,7 @@
       <c r="DX80" t="inlineStr"/>
       <c r="DY80" t="inlineStr"/>
       <c r="DZ80" t="inlineStr"/>
+      <c r="EA80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -19649,7 +19733,7 @@
       <c r="N81" t="n">
         <v>325</v>
       </c>
-      <c r="O81" t="b">
+      <c r="O81" t="n">
         <v>0</v>
       </c>
       <c r="P81" t="n">
@@ -19831,6 +19915,7 @@
       <c r="DX81" t="inlineStr"/>
       <c r="DY81" t="inlineStr"/>
       <c r="DZ81" t="inlineStr"/>
+      <c r="EA81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -19884,7 +19969,7 @@
       <c r="N82" t="n">
         <v>325</v>
       </c>
-      <c r="O82" t="b">
+      <c r="O82" t="n">
         <v>0</v>
       </c>
       <c r="P82" t="n">
@@ -20066,6 +20151,7 @@
       <c r="DX82" t="inlineStr"/>
       <c r="DY82" t="inlineStr"/>
       <c r="DZ82" t="inlineStr"/>
+      <c r="EA82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -20119,7 +20205,7 @@
       <c r="N83" t="n">
         <v>325</v>
       </c>
-      <c r="O83" t="b">
+      <c r="O83" t="n">
         <v>0</v>
       </c>
       <c r="P83" t="n">
@@ -20301,6 +20387,7 @@
       <c r="DX83" t="inlineStr"/>
       <c r="DY83" t="inlineStr"/>
       <c r="DZ83" t="inlineStr"/>
+      <c r="EA83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -20354,7 +20441,7 @@
       <c r="N84" t="n">
         <v>325</v>
       </c>
-      <c r="O84" t="b">
+      <c r="O84" t="n">
         <v>0</v>
       </c>
       <c r="P84" t="n">
@@ -20536,6 +20623,7 @@
       <c r="DX84" t="inlineStr"/>
       <c r="DY84" t="inlineStr"/>
       <c r="DZ84" t="inlineStr"/>
+      <c r="EA84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -20589,7 +20677,7 @@
       <c r="N85" t="n">
         <v>245</v>
       </c>
-      <c r="O85" t="b">
+      <c r="O85" t="n">
         <v>0</v>
       </c>
       <c r="P85" t="n">
@@ -20771,6 +20859,7 @@
       <c r="DX85" t="inlineStr"/>
       <c r="DY85" t="inlineStr"/>
       <c r="DZ85" t="inlineStr"/>
+      <c r="EA85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -20824,7 +20913,7 @@
       <c r="N86" t="n">
         <v>245</v>
       </c>
-      <c r="O86" t="b">
+      <c r="O86" t="n">
         <v>0</v>
       </c>
       <c r="P86" t="n">
@@ -21006,6 +21095,7 @@
       <c r="DX86" t="inlineStr"/>
       <c r="DY86" t="inlineStr"/>
       <c r="DZ86" t="inlineStr"/>
+      <c r="EA86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -21059,7 +21149,7 @@
       <c r="N87" t="n">
         <v>245</v>
       </c>
-      <c r="O87" t="b">
+      <c r="O87" t="n">
         <v>0</v>
       </c>
       <c r="P87" t="n">
@@ -21241,6 +21331,7 @@
       <c r="DX87" t="inlineStr"/>
       <c r="DY87" t="inlineStr"/>
       <c r="DZ87" t="inlineStr"/>
+      <c r="EA87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -21294,7 +21385,7 @@
       <c r="N88" t="n">
         <v>245</v>
       </c>
-      <c r="O88" t="b">
+      <c r="O88" t="n">
         <v>0</v>
       </c>
       <c r="P88" t="n">
@@ -21476,6 +21567,7 @@
       <c r="DX88" t="inlineStr"/>
       <c r="DY88" t="inlineStr"/>
       <c r="DZ88" t="inlineStr"/>
+      <c r="EA88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -21529,7 +21621,7 @@
       <c r="N89" t="n">
         <v>245</v>
       </c>
-      <c r="O89" t="b">
+      <c r="O89" t="n">
         <v>0</v>
       </c>
       <c r="P89" t="n">
@@ -21711,6 +21803,7 @@
       <c r="DX89" t="inlineStr"/>
       <c r="DY89" t="inlineStr"/>
       <c r="DZ89" t="inlineStr"/>
+      <c r="EA89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -21764,7 +21857,7 @@
       <c r="N90" t="n">
         <v>25</v>
       </c>
-      <c r="O90" t="b">
+      <c r="O90" t="n">
         <v>0</v>
       </c>
       <c r="P90" t="n">
@@ -21946,6 +22039,7 @@
       <c r="DX90" t="inlineStr"/>
       <c r="DY90" t="inlineStr"/>
       <c r="DZ90" t="inlineStr"/>
+      <c r="EA90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -21999,7 +22093,7 @@
       <c r="N91" t="n">
         <v>25</v>
       </c>
-      <c r="O91" t="b">
+      <c r="O91" t="n">
         <v>0</v>
       </c>
       <c r="P91" t="n">
@@ -22181,6 +22275,7 @@
       <c r="DX91" t="inlineStr"/>
       <c r="DY91" t="inlineStr"/>
       <c r="DZ91" t="inlineStr"/>
+      <c r="EA91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -22234,7 +22329,7 @@
       <c r="N92" t="n">
         <v>25</v>
       </c>
-      <c r="O92" t="b">
+      <c r="O92" t="n">
         <v>0</v>
       </c>
       <c r="P92" t="n">
@@ -22416,6 +22511,7 @@
       <c r="DX92" t="inlineStr"/>
       <c r="DY92" t="inlineStr"/>
       <c r="DZ92" t="inlineStr"/>
+      <c r="EA92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -22469,7 +22565,7 @@
       <c r="N93" t="n">
         <v>25</v>
       </c>
-      <c r="O93" t="b">
+      <c r="O93" t="n">
         <v>0</v>
       </c>
       <c r="P93" t="n">
@@ -22651,6 +22747,7 @@
       <c r="DX93" t="inlineStr"/>
       <c r="DY93" t="inlineStr"/>
       <c r="DZ93" t="inlineStr"/>
+      <c r="EA93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -22704,7 +22801,7 @@
       <c r="N94" t="n">
         <v>285</v>
       </c>
-      <c r="O94" t="b">
+      <c r="O94" t="n">
         <v>0</v>
       </c>
       <c r="P94" t="n">
@@ -22886,6 +22983,7 @@
       <c r="DX94" t="inlineStr"/>
       <c r="DY94" t="inlineStr"/>
       <c r="DZ94" t="inlineStr"/>
+      <c r="EA94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -22939,7 +23037,7 @@
       <c r="N95" t="n">
         <v>83</v>
       </c>
-      <c r="O95" t="b">
+      <c r="O95" t="n">
         <v>0</v>
       </c>
       <c r="P95" t="n">
@@ -23121,6 +23219,7 @@
       <c r="DX95" t="inlineStr"/>
       <c r="DY95" t="inlineStr"/>
       <c r="DZ95" t="inlineStr"/>
+      <c r="EA95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -23174,7 +23273,7 @@
       <c r="N96" t="n">
         <v>473</v>
       </c>
-      <c r="O96" t="b">
+      <c r="O96" t="n">
         <v>0</v>
       </c>
       <c r="P96" t="n">
@@ -23356,6 +23455,7 @@
       <c r="DX96" t="inlineStr"/>
       <c r="DY96" t="inlineStr"/>
       <c r="DZ96" t="inlineStr"/>
+      <c r="EA96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -23409,7 +23509,7 @@
       <c r="N97" t="n">
         <v>473</v>
       </c>
-      <c r="O97" t="b">
+      <c r="O97" t="n">
         <v>0</v>
       </c>
       <c r="P97" t="n">
@@ -23591,6 +23691,7 @@
       <c r="DX97" t="inlineStr"/>
       <c r="DY97" t="inlineStr"/>
       <c r="DZ97" t="inlineStr"/>
+      <c r="EA97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -23644,7 +23745,7 @@
       <c r="N98" t="n">
         <v>473</v>
       </c>
-      <c r="O98" t="b">
+      <c r="O98" t="n">
         <v>0</v>
       </c>
       <c r="P98" t="n">
@@ -23826,6 +23927,7 @@
       <c r="DX98" t="inlineStr"/>
       <c r="DY98" t="inlineStr"/>
       <c r="DZ98" t="inlineStr"/>
+      <c r="EA98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -23879,7 +23981,7 @@
       <c r="N99" t="n">
         <v>473</v>
       </c>
-      <c r="O99" t="b">
+      <c r="O99" t="n">
         <v>0</v>
       </c>
       <c r="P99" t="n">
@@ -24061,6 +24163,7 @@
       <c r="DX99" t="inlineStr"/>
       <c r="DY99" t="inlineStr"/>
       <c r="DZ99" t="inlineStr"/>
+      <c r="EA99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -24114,7 +24217,7 @@
       <c r="N100" t="n">
         <v>473</v>
       </c>
-      <c r="O100" t="b">
+      <c r="O100" t="n">
         <v>0</v>
       </c>
       <c r="P100" t="n">
@@ -24296,6 +24399,7 @@
       <c r="DX100" t="inlineStr"/>
       <c r="DY100" t="inlineStr"/>
       <c r="DZ100" t="inlineStr"/>
+      <c r="EA100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -24349,7 +24453,7 @@
       <c r="N101" t="n">
         <v>473</v>
       </c>
-      <c r="O101" t="b">
+      <c r="O101" t="n">
         <v>0</v>
       </c>
       <c r="P101" t="n">
@@ -24531,6 +24635,7 @@
       <c r="DX101" t="inlineStr"/>
       <c r="DY101" t="inlineStr"/>
       <c r="DZ101" t="inlineStr"/>
+      <c r="EA101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -24584,7 +24689,7 @@
       <c r="N102" t="n">
         <v>473</v>
       </c>
-      <c r="O102" t="b">
+      <c r="O102" t="n">
         <v>0</v>
       </c>
       <c r="P102" t="n">
@@ -24766,6 +24871,7 @@
       <c r="DX102" t="inlineStr"/>
       <c r="DY102" t="inlineStr"/>
       <c r="DZ102" t="inlineStr"/>
+      <c r="EA102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -24819,7 +24925,7 @@
       <c r="N103" t="n">
         <v>73</v>
       </c>
-      <c r="O103" t="b">
+      <c r="O103" t="n">
         <v>0</v>
       </c>
       <c r="P103" t="n">
@@ -25001,6 +25107,7 @@
       <c r="DX103" t="inlineStr"/>
       <c r="DY103" t="inlineStr"/>
       <c r="DZ103" t="inlineStr"/>
+      <c r="EA103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -25054,7 +25161,7 @@
       <c r="N104" t="n">
         <v>73</v>
       </c>
-      <c r="O104" t="b">
+      <c r="O104" t="n">
         <v>0</v>
       </c>
       <c r="P104" t="n">
@@ -25236,6 +25343,7 @@
       <c r="DX104" t="inlineStr"/>
       <c r="DY104" t="inlineStr"/>
       <c r="DZ104" t="inlineStr"/>
+      <c r="EA104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -25289,7 +25397,7 @@
       <c r="N105" t="n">
         <v>73</v>
       </c>
-      <c r="O105" t="b">
+      <c r="O105" t="n">
         <v>0</v>
       </c>
       <c r="P105" t="n">
@@ -25471,6 +25579,7 @@
       <c r="DX105" t="inlineStr"/>
       <c r="DY105" t="inlineStr"/>
       <c r="DZ105" t="inlineStr"/>
+      <c r="EA105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -25524,7 +25633,7 @@
       <c r="N106" t="n">
         <v>73</v>
       </c>
-      <c r="O106" t="b">
+      <c r="O106" t="n">
         <v>0</v>
       </c>
       <c r="P106" t="n">
@@ -25706,6 +25815,7 @@
       <c r="DX106" t="inlineStr"/>
       <c r="DY106" t="inlineStr"/>
       <c r="DZ106" t="inlineStr"/>
+      <c r="EA106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -25759,7 +25869,7 @@
       <c r="N107" t="n">
         <v>73</v>
       </c>
-      <c r="O107" t="b">
+      <c r="O107" t="n">
         <v>0</v>
       </c>
       <c r="P107" t="n">
@@ -25941,6 +26051,7 @@
       <c r="DX107" t="inlineStr"/>
       <c r="DY107" t="inlineStr"/>
       <c r="DZ107" t="inlineStr"/>
+      <c r="EA107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -25994,7 +26105,7 @@
       <c r="N108" t="n">
         <v>73</v>
       </c>
-      <c r="O108" t="b">
+      <c r="O108" t="n">
         <v>0</v>
       </c>
       <c r="P108" t="n">
@@ -26176,6 +26287,7 @@
       <c r="DX108" t="inlineStr"/>
       <c r="DY108" t="inlineStr"/>
       <c r="DZ108" t="inlineStr"/>
+      <c r="EA108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -26229,7 +26341,7 @@
       <c r="N109" t="n">
         <v>173</v>
       </c>
-      <c r="O109" t="b">
+      <c r="O109" t="n">
         <v>0</v>
       </c>
       <c r="P109" t="n">
@@ -26411,6 +26523,7 @@
       <c r="DX109" t="inlineStr"/>
       <c r="DY109" t="inlineStr"/>
       <c r="DZ109" t="inlineStr"/>
+      <c r="EA109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -26464,7 +26577,7 @@
       <c r="N110" t="n">
         <v>173</v>
       </c>
-      <c r="O110" t="b">
+      <c r="O110" t="n">
         <v>0</v>
       </c>
       <c r="P110" t="n">
@@ -26646,6 +26759,7 @@
       <c r="DX110" t="inlineStr"/>
       <c r="DY110" t="inlineStr"/>
       <c r="DZ110" t="inlineStr"/>
+      <c r="EA110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -26699,7 +26813,7 @@
       <c r="N111" t="n">
         <v>73</v>
       </c>
-      <c r="O111" t="b">
+      <c r="O111" t="n">
         <v>0</v>
       </c>
       <c r="P111" t="n">
@@ -26881,6 +26995,7 @@
       <c r="DX111" t="inlineStr"/>
       <c r="DY111" t="inlineStr"/>
       <c r="DZ111" t="inlineStr"/>
+      <c r="EA111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -26934,7 +27049,7 @@
       <c r="N112" t="n">
         <v>73</v>
       </c>
-      <c r="O112" t="b">
+      <c r="O112" t="n">
         <v>0</v>
       </c>
       <c r="P112" t="n">
@@ -27116,6 +27231,7 @@
       <c r="DX112" t="inlineStr"/>
       <c r="DY112" t="inlineStr"/>
       <c r="DZ112" t="inlineStr"/>
+      <c r="EA112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -27169,7 +27285,7 @@
       <c r="N113" t="n">
         <v>73</v>
       </c>
-      <c r="O113" t="b">
+      <c r="O113" t="n">
         <v>0</v>
       </c>
       <c r="P113" t="n">
@@ -27351,6 +27467,7 @@
       <c r="DX113" t="inlineStr"/>
       <c r="DY113" t="inlineStr"/>
       <c r="DZ113" t="inlineStr"/>
+      <c r="EA113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -27404,7 +27521,7 @@
       <c r="N114" t="n">
         <v>73</v>
       </c>
-      <c r="O114" t="b">
+      <c r="O114" t="n">
         <v>0</v>
       </c>
       <c r="P114" t="n">
@@ -27586,6 +27703,7 @@
       <c r="DX114" t="inlineStr"/>
       <c r="DY114" t="inlineStr"/>
       <c r="DZ114" t="inlineStr"/>
+      <c r="EA114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -27639,7 +27757,7 @@
       <c r="N115" t="n">
         <v>13</v>
       </c>
-      <c r="O115" t="b">
+      <c r="O115" t="n">
         <v>0</v>
       </c>
       <c r="P115" t="n">
@@ -27821,6 +27939,7 @@
       <c r="DX115" t="inlineStr"/>
       <c r="DY115" t="inlineStr"/>
       <c r="DZ115" t="inlineStr"/>
+      <c r="EA115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -27874,7 +27993,7 @@
       <c r="N116" t="n">
         <v>13</v>
       </c>
-      <c r="O116" t="b">
+      <c r="O116" t="n">
         <v>0</v>
       </c>
       <c r="P116" t="n">
@@ -28056,6 +28175,7 @@
       <c r="DX116" t="inlineStr"/>
       <c r="DY116" t="inlineStr"/>
       <c r="DZ116" t="inlineStr"/>
+      <c r="EA116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -28109,7 +28229,7 @@
       <c r="N117" t="n">
         <v>13</v>
       </c>
-      <c r="O117" t="b">
+      <c r="O117" t="n">
         <v>0</v>
       </c>
       <c r="P117" t="n">
@@ -28291,6 +28411,7 @@
       <c r="DX117" t="inlineStr"/>
       <c r="DY117" t="inlineStr"/>
       <c r="DZ117" t="inlineStr"/>
+      <c r="EA117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -28344,7 +28465,7 @@
       <c r="N118" t="n">
         <v>13</v>
       </c>
-      <c r="O118" t="b">
+      <c r="O118" t="n">
         <v>0</v>
       </c>
       <c r="P118" t="n">
@@ -28526,6 +28647,7 @@
       <c r="DX118" t="inlineStr"/>
       <c r="DY118" t="inlineStr"/>
       <c r="DZ118" t="inlineStr"/>
+      <c r="EA118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -28579,7 +28701,7 @@
       <c r="N119" t="n">
         <v>113</v>
       </c>
-      <c r="O119" t="b">
+      <c r="O119" t="n">
         <v>0</v>
       </c>
       <c r="P119" t="n">
@@ -28761,6 +28883,7 @@
       <c r="DX119" t="inlineStr"/>
       <c r="DY119" t="inlineStr"/>
       <c r="DZ119" t="inlineStr"/>
+      <c r="EA119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -28814,7 +28937,7 @@
       <c r="N120" t="n">
         <v>123</v>
       </c>
-      <c r="O120" t="b">
+      <c r="O120" t="n">
         <v>0</v>
       </c>
       <c r="P120" t="n">
@@ -28996,6 +29119,7 @@
       <c r="DX120" t="inlineStr"/>
       <c r="DY120" t="inlineStr"/>
       <c r="DZ120" t="inlineStr"/>
+      <c r="EA120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -29049,7 +29173,7 @@
       <c r="N121" t="n">
         <v>23</v>
       </c>
-      <c r="O121" t="b">
+      <c r="O121" t="n">
         <v>0</v>
       </c>
       <c r="P121" t="n">
@@ -29231,6 +29355,7 @@
       <c r="DX121" t="inlineStr"/>
       <c r="DY121" t="inlineStr"/>
       <c r="DZ121" t="inlineStr"/>
+      <c r="EA121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -29284,7 +29409,7 @@
       <c r="N122" t="n">
         <v>23</v>
       </c>
-      <c r="O122" t="b">
+      <c r="O122" t="n">
         <v>0</v>
       </c>
       <c r="P122" t="n">
@@ -29466,6 +29591,7 @@
       <c r="DX122" t="inlineStr"/>
       <c r="DY122" t="inlineStr"/>
       <c r="DZ122" t="inlineStr"/>
+      <c r="EA122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -29519,7 +29645,7 @@
       <c r="N123" t="n">
         <v>23</v>
       </c>
-      <c r="O123" t="b">
+      <c r="O123" t="n">
         <v>0</v>
       </c>
       <c r="P123" t="n">
@@ -29701,6 +29827,7 @@
       <c r="DX123" t="inlineStr"/>
       <c r="DY123" t="inlineStr"/>
       <c r="DZ123" t="inlineStr"/>
+      <c r="EA123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -29754,7 +29881,7 @@
       <c r="N124" t="n">
         <v>23</v>
       </c>
-      <c r="O124" t="b">
+      <c r="O124" t="n">
         <v>0</v>
       </c>
       <c r="P124" t="n">
@@ -29936,6 +30063,7 @@
       <c r="DX124" t="inlineStr"/>
       <c r="DY124" t="inlineStr"/>
       <c r="DZ124" t="inlineStr"/>
+      <c r="EA124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -29989,7 +30117,7 @@
       <c r="N125" t="n">
         <v>23</v>
       </c>
-      <c r="O125" t="b">
+      <c r="O125" t="n">
         <v>0</v>
       </c>
       <c r="P125" t="n">
@@ -30171,6 +30299,7 @@
       <c r="DX125" t="inlineStr"/>
       <c r="DY125" t="inlineStr"/>
       <c r="DZ125" t="inlineStr"/>
+      <c r="EA125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -30224,7 +30353,7 @@
       <c r="N126" t="n">
         <v>253</v>
       </c>
-      <c r="O126" t="b">
+      <c r="O126" t="n">
         <v>0</v>
       </c>
       <c r="P126" t="n">
@@ -30406,6 +30535,7 @@
       <c r="DX126" t="inlineStr"/>
       <c r="DY126" t="inlineStr"/>
       <c r="DZ126" t="inlineStr"/>
+      <c r="EA126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -30459,7 +30589,7 @@
       <c r="N127" t="n">
         <v>253</v>
       </c>
-      <c r="O127" t="b">
+      <c r="O127" t="n">
         <v>0</v>
       </c>
       <c r="P127" t="n">
@@ -30641,6 +30771,7 @@
       <c r="DX127" t="inlineStr"/>
       <c r="DY127" t="inlineStr"/>
       <c r="DZ127" t="inlineStr"/>
+      <c r="EA127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -30694,7 +30825,7 @@
       <c r="N128" t="n">
         <v>23</v>
       </c>
-      <c r="O128" t="b">
+      <c r="O128" t="n">
         <v>0</v>
       </c>
       <c r="P128" t="n">
@@ -30876,6 +31007,7 @@
       <c r="DX128" t="inlineStr"/>
       <c r="DY128" t="inlineStr"/>
       <c r="DZ128" t="inlineStr"/>
+      <c r="EA128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -30929,7 +31061,7 @@
       <c r="N129" t="n">
         <v>23</v>
       </c>
-      <c r="O129" t="b">
+      <c r="O129" t="n">
         <v>0</v>
       </c>
       <c r="P129" t="n">
@@ -31111,6 +31243,7 @@
       <c r="DX129" t="inlineStr"/>
       <c r="DY129" t="inlineStr"/>
       <c r="DZ129" t="inlineStr"/>
+      <c r="EA129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -31164,7 +31297,7 @@
       <c r="N130" t="n">
         <v>23</v>
       </c>
-      <c r="O130" t="b">
+      <c r="O130" t="n">
         <v>0</v>
       </c>
       <c r="P130" t="n">
@@ -31346,6 +31479,7 @@
       <c r="DX130" t="inlineStr"/>
       <c r="DY130" t="inlineStr"/>
       <c r="DZ130" t="inlineStr"/>
+      <c r="EA130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -31399,7 +31533,7 @@
       <c r="N131" t="n">
         <v>23</v>
       </c>
-      <c r="O131" t="b">
+      <c r="O131" t="n">
         <v>0</v>
       </c>
       <c r="P131" t="n">
@@ -31581,6 +31715,7 @@
       <c r="DX131" t="inlineStr"/>
       <c r="DY131" t="inlineStr"/>
       <c r="DZ131" t="inlineStr"/>
+      <c r="EA131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -31634,7 +31769,7 @@
       <c r="N132" t="n">
         <v>23</v>
       </c>
-      <c r="O132" t="b">
+      <c r="O132" t="n">
         <v>0</v>
       </c>
       <c r="P132" t="n">
@@ -31816,6 +31951,7 @@
       <c r="DX132" t="inlineStr"/>
       <c r="DY132" t="inlineStr"/>
       <c r="DZ132" t="inlineStr"/>
+      <c r="EA132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -31869,7 +32005,7 @@
       <c r="N133" t="n">
         <v>28</v>
       </c>
-      <c r="O133" t="b">
+      <c r="O133" t="n">
         <v>0</v>
       </c>
       <c r="P133" t="n">
@@ -32051,6 +32187,7 @@
       <c r="DX133" t="inlineStr"/>
       <c r="DY133" t="inlineStr"/>
       <c r="DZ133" t="inlineStr"/>
+      <c r="EA133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -32104,7 +32241,7 @@
       <c r="N134" t="n">
         <v>28</v>
       </c>
-      <c r="O134" t="b">
+      <c r="O134" t="n">
         <v>0</v>
       </c>
       <c r="P134" t="n">
@@ -32286,6 +32423,7 @@
       <c r="DX134" t="inlineStr"/>
       <c r="DY134" t="inlineStr"/>
       <c r="DZ134" t="inlineStr"/>
+      <c r="EA134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -32339,7 +32477,7 @@
       <c r="N135" t="n">
         <v>218</v>
       </c>
-      <c r="O135" t="b">
+      <c r="O135" t="n">
         <v>0</v>
       </c>
       <c r="P135" t="n">
@@ -32521,6 +32659,7 @@
       <c r="DX135" t="inlineStr"/>
       <c r="DY135" t="inlineStr"/>
       <c r="DZ135" t="inlineStr"/>
+      <c r="EA135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -32574,7 +32713,7 @@
       <c r="N136" t="n">
         <v>228</v>
       </c>
-      <c r="O136" t="b">
+      <c r="O136" t="n">
         <v>0</v>
       </c>
       <c r="P136" t="n">
@@ -32756,6 +32895,7 @@
       <c r="DX136" t="inlineStr"/>
       <c r="DY136" t="inlineStr"/>
       <c r="DZ136" t="inlineStr"/>
+      <c r="EA136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -32810,7 +32950,7 @@
       <c r="N137" t="n">
         <v>228</v>
       </c>
-      <c r="O137" t="b">
+      <c r="O137" t="n">
         <v>0</v>
       </c>
       <c r="P137" t="n">
@@ -32992,6 +33132,7 @@
       <c r="DX137" t="inlineStr"/>
       <c r="DY137" t="inlineStr"/>
       <c r="DZ137" t="inlineStr"/>
+      <c r="EA137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -33046,7 +33187,7 @@
       <c r="N138" t="n">
         <v>228</v>
       </c>
-      <c r="O138" t="b">
+      <c r="O138" t="n">
         <v>0</v>
       </c>
       <c r="P138" t="n">
@@ -33228,6 +33369,7 @@
       <c r="DX138" t="inlineStr"/>
       <c r="DY138" t="inlineStr"/>
       <c r="DZ138" t="inlineStr"/>
+      <c r="EA138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -33281,7 +33423,7 @@
       <c r="N139" t="n">
         <v>228</v>
       </c>
-      <c r="O139" t="b">
+      <c r="O139" t="n">
         <v>0</v>
       </c>
       <c r="P139" t="n">
@@ -33463,6 +33605,7 @@
       <c r="DX139" t="inlineStr"/>
       <c r="DY139" t="inlineStr"/>
       <c r="DZ139" t="inlineStr"/>
+      <c r="EA139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -33516,7 +33659,7 @@
       <c r="N140" t="n">
         <v>238</v>
       </c>
-      <c r="O140" t="b">
+      <c r="O140" t="n">
         <v>0</v>
       </c>
       <c r="P140" t="n">
@@ -33698,6 +33841,7 @@
       <c r="DX140" t="inlineStr"/>
       <c r="DY140" t="inlineStr"/>
       <c r="DZ140" t="inlineStr"/>
+      <c r="EA140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -33751,7 +33895,7 @@
       <c r="N141" t="n">
         <v>238</v>
       </c>
-      <c r="O141" t="b">
+      <c r="O141" t="n">
         <v>0</v>
       </c>
       <c r="P141" t="n">
@@ -33933,6 +34077,7 @@
       <c r="DX141" t="inlineStr"/>
       <c r="DY141" t="inlineStr"/>
       <c r="DZ141" t="inlineStr"/>
+      <c r="EA141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -33986,7 +34131,7 @@
       <c r="N142" t="n">
         <v>238</v>
       </c>
-      <c r="O142" t="b">
+      <c r="O142" t="n">
         <v>0</v>
       </c>
       <c r="P142" t="n">
@@ -34168,6 +34313,7 @@
       <c r="DX142" t="inlineStr"/>
       <c r="DY142" t="inlineStr"/>
       <c r="DZ142" t="inlineStr"/>
+      <c r="EA142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -34221,7 +34367,7 @@
       <c r="N143" t="n">
         <v>238</v>
       </c>
-      <c r="O143" t="b">
+      <c r="O143" t="n">
         <v>0</v>
       </c>
       <c r="P143" t="n">
@@ -34403,6 +34549,7 @@
       <c r="DX143" t="inlineStr"/>
       <c r="DY143" t="inlineStr"/>
       <c r="DZ143" t="inlineStr"/>
+      <c r="EA143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -34456,7 +34603,7 @@
       <c r="N144" t="n">
         <v>228</v>
       </c>
-      <c r="O144" t="b">
+      <c r="O144" t="n">
         <v>0</v>
       </c>
       <c r="P144" t="n">
@@ -34638,6 +34785,7 @@
       <c r="DX144" t="inlineStr"/>
       <c r="DY144" t="inlineStr"/>
       <c r="DZ144" t="inlineStr"/>
+      <c r="EA144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -34691,7 +34839,7 @@
       <c r="N145" t="n">
         <v>228</v>
       </c>
-      <c r="O145" t="b">
+      <c r="O145" t="n">
         <v>0</v>
       </c>
       <c r="P145" t="n">
@@ -34873,6 +35021,7 @@
       <c r="DX145" t="inlineStr"/>
       <c r="DY145" t="inlineStr"/>
       <c r="DZ145" t="inlineStr"/>
+      <c r="EA145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -34926,7 +35075,7 @@
       <c r="N146" t="n">
         <v>228</v>
       </c>
-      <c r="O146" t="b">
+      <c r="O146" t="n">
         <v>0</v>
       </c>
       <c r="P146" t="n">
@@ -35108,6 +35257,7 @@
       <c r="DX146" t="inlineStr"/>
       <c r="DY146" t="inlineStr"/>
       <c r="DZ146" t="inlineStr"/>
+      <c r="EA146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -35161,7 +35311,7 @@
       <c r="N147" t="n">
         <v>228</v>
       </c>
-      <c r="O147" t="b">
+      <c r="O147" t="n">
         <v>0</v>
       </c>
       <c r="P147" t="n">
@@ -35343,6 +35493,7 @@
       <c r="DX147" t="inlineStr"/>
       <c r="DY147" t="inlineStr"/>
       <c r="DZ147" t="inlineStr"/>
+      <c r="EA147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -35396,7 +35547,7 @@
       <c r="N148" t="n">
         <v>228</v>
       </c>
-      <c r="O148" t="b">
+      <c r="O148" t="n">
         <v>0</v>
       </c>
       <c r="P148" t="n">
@@ -35578,6 +35729,7 @@
       <c r="DX148" t="inlineStr"/>
       <c r="DY148" t="inlineStr"/>
       <c r="DZ148" t="inlineStr"/>
+      <c r="EA148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -35631,7 +35783,7 @@
       <c r="N149" t="n">
         <v>228</v>
       </c>
-      <c r="O149" t="b">
+      <c r="O149" t="n">
         <v>0</v>
       </c>
       <c r="P149" t="n">
@@ -35813,6 +35965,7 @@
       <c r="DX149" t="inlineStr"/>
       <c r="DY149" t="inlineStr"/>
       <c r="DZ149" t="inlineStr"/>
+      <c r="EA149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -35866,7 +36019,7 @@
       <c r="N150" t="n">
         <v>228</v>
       </c>
-      <c r="O150" t="b">
+      <c r="O150" t="n">
         <v>0</v>
       </c>
       <c r="P150" t="n">
@@ -36048,6 +36201,7 @@
       <c r="DX150" t="inlineStr"/>
       <c r="DY150" t="inlineStr"/>
       <c r="DZ150" t="inlineStr"/>
+      <c r="EA150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -36101,7 +36255,7 @@
       <c r="N151" t="n">
         <v>228</v>
       </c>
-      <c r="O151" t="b">
+      <c r="O151" t="n">
         <v>0</v>
       </c>
       <c r="P151" t="n">
@@ -36283,6 +36437,7 @@
       <c r="DX151" t="inlineStr"/>
       <c r="DY151" t="inlineStr"/>
       <c r="DZ151" t="inlineStr"/>
+      <c r="EA151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -36336,7 +36491,7 @@
       <c r="N152" t="n">
         <v>228</v>
       </c>
-      <c r="O152" t="b">
+      <c r="O152" t="n">
         <v>0</v>
       </c>
       <c r="P152" t="n">
@@ -36518,6 +36673,7 @@
       <c r="DX152" t="inlineStr"/>
       <c r="DY152" t="inlineStr"/>
       <c r="DZ152" t="inlineStr"/>
+      <c r="EA152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -36571,7 +36727,7 @@
       <c r="N153" t="n">
         <v>278</v>
       </c>
-      <c r="O153" t="b">
+      <c r="O153" t="n">
         <v>0</v>
       </c>
       <c r="P153" t="n">
@@ -36753,6 +36909,7 @@
       <c r="DX153" t="inlineStr"/>
       <c r="DY153" t="inlineStr"/>
       <c r="DZ153" t="inlineStr"/>
+      <c r="EA153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -36806,7 +36963,7 @@
       <c r="N154" t="n">
         <v>278</v>
       </c>
-      <c r="O154" t="b">
+      <c r="O154" t="n">
         <v>0</v>
       </c>
       <c r="P154" t="n">
@@ -36988,6 +37145,7 @@
       <c r="DX154" t="inlineStr"/>
       <c r="DY154" t="inlineStr"/>
       <c r="DZ154" t="inlineStr"/>
+      <c r="EA154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -37041,7 +37199,7 @@
       <c r="N155" t="n">
         <v>278</v>
       </c>
-      <c r="O155" t="b">
+      <c r="O155" t="n">
         <v>0</v>
       </c>
       <c r="P155" t="n">
@@ -37223,6 +37381,7 @@
       <c r="DX155" t="inlineStr"/>
       <c r="DY155" t="inlineStr"/>
       <c r="DZ155" t="inlineStr"/>
+      <c r="EA155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -37276,7 +37435,7 @@
       <c r="N156" t="n">
         <v>278</v>
       </c>
-      <c r="O156" t="b">
+      <c r="O156" t="n">
         <v>0</v>
       </c>
       <c r="P156" t="n">
@@ -37458,6 +37617,7 @@
       <c r="DX156" t="inlineStr"/>
       <c r="DY156" t="inlineStr"/>
       <c r="DZ156" t="inlineStr"/>
+      <c r="EA156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -37511,7 +37671,7 @@
       <c r="N157" t="n">
         <v>278</v>
       </c>
-      <c r="O157" t="b">
+      <c r="O157" t="n">
         <v>0</v>
       </c>
       <c r="P157" t="n">
@@ -37693,6 +37853,7 @@
       <c r="DX157" t="inlineStr"/>
       <c r="DY157" t="inlineStr"/>
       <c r="DZ157" t="inlineStr"/>
+      <c r="EA157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -37746,7 +37907,7 @@
       <c r="N158" t="n">
         <v>278</v>
       </c>
-      <c r="O158" t="b">
+      <c r="O158" t="n">
         <v>0</v>
       </c>
       <c r="P158" t="n">
@@ -37928,6 +38089,7 @@
       <c r="DX158" t="inlineStr"/>
       <c r="DY158" t="inlineStr"/>
       <c r="DZ158" t="inlineStr"/>
+      <c r="EA158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -37981,7 +38143,7 @@
       <c r="N159" t="n">
         <v>278</v>
       </c>
-      <c r="O159" t="b">
+      <c r="O159" t="n">
         <v>0</v>
       </c>
       <c r="P159" t="n">
@@ -38163,6 +38325,7 @@
       <c r="DX159" t="inlineStr"/>
       <c r="DY159" t="inlineStr"/>
       <c r="DZ159" t="inlineStr"/>
+      <c r="EA159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -38216,7 +38379,7 @@
       <c r="N160" t="n">
         <v>228</v>
       </c>
-      <c r="O160" t="b">
+      <c r="O160" t="n">
         <v>0</v>
       </c>
       <c r="P160" t="n">
@@ -38398,6 +38561,7 @@
       <c r="DX160" t="inlineStr"/>
       <c r="DY160" t="inlineStr"/>
       <c r="DZ160" t="inlineStr"/>
+      <c r="EA160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -38451,7 +38615,7 @@
       <c r="N161" t="n">
         <v>228</v>
       </c>
-      <c r="O161" t="b">
+      <c r="O161" t="n">
         <v>0</v>
       </c>
       <c r="P161" t="n">
@@ -38633,6 +38797,7 @@
       <c r="DX161" t="inlineStr"/>
       <c r="DY161" t="inlineStr"/>
       <c r="DZ161" t="inlineStr"/>
+      <c r="EA161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -38686,7 +38851,7 @@
       <c r="N162" t="n">
         <v>228</v>
       </c>
-      <c r="O162" t="b">
+      <c r="O162" t="n">
         <v>0</v>
       </c>
       <c r="P162" t="n">
@@ -38868,6 +39033,7 @@
       <c r="DX162" t="inlineStr"/>
       <c r="DY162" t="inlineStr"/>
       <c r="DZ162" t="inlineStr"/>
+      <c r="EA162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -38921,7 +39087,7 @@
       <c r="N163" t="n">
         <v>128</v>
       </c>
-      <c r="O163" t="b">
+      <c r="O163" t="n">
         <v>0</v>
       </c>
       <c r="P163" t="n">
@@ -39103,6 +39269,7 @@
       <c r="DX163" t="inlineStr"/>
       <c r="DY163" t="inlineStr"/>
       <c r="DZ163" t="inlineStr"/>
+      <c r="EA163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -39156,7 +39323,7 @@
       <c r="N164" t="n">
         <v>178</v>
       </c>
-      <c r="O164" t="b">
+      <c r="O164" t="n">
         <v>0</v>
       </c>
       <c r="P164" t="n">
@@ -39338,6 +39505,7 @@
       <c r="DX164" t="inlineStr"/>
       <c r="DY164" t="inlineStr"/>
       <c r="DZ164" t="inlineStr"/>
+      <c r="EA164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -39391,7 +39559,7 @@
       <c r="N165" t="n">
         <v>7</v>
       </c>
-      <c r="O165" t="b">
+      <c r="O165" t="n">
         <v>0</v>
       </c>
       <c r="P165" t="n">
@@ -39573,6 +39741,7 @@
       <c r="DX165" t="inlineStr"/>
       <c r="DY165" t="inlineStr"/>
       <c r="DZ165" t="inlineStr"/>
+      <c r="EA165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -39626,7 +39795,7 @@
       <c r="N166" t="n">
         <v>9</v>
       </c>
-      <c r="O166" t="b">
+      <c r="O166" t="n">
         <v>0</v>
       </c>
       <c r="P166" t="n">
@@ -39808,6 +39977,7 @@
       <c r="DX166" t="inlineStr"/>
       <c r="DY166" t="inlineStr"/>
       <c r="DZ166" t="inlineStr"/>
+      <c r="EA166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -39861,7 +40031,7 @@
       <c r="N167" t="n">
         <v>9</v>
       </c>
-      <c r="O167" t="b">
+      <c r="O167" t="n">
         <v>0</v>
       </c>
       <c r="P167" t="n">
@@ -40043,6 +40213,7 @@
       <c r="DX167" t="inlineStr"/>
       <c r="DY167" t="inlineStr"/>
       <c r="DZ167" t="inlineStr"/>
+      <c r="EA167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -40096,7 +40267,7 @@
       <c r="N168" t="n">
         <v>9</v>
       </c>
-      <c r="O168" t="b">
+      <c r="O168" t="n">
         <v>0</v>
       </c>
       <c r="P168" t="n">
@@ -40278,6 +40449,7 @@
       <c r="DX168" t="inlineStr"/>
       <c r="DY168" t="inlineStr"/>
       <c r="DZ168" t="inlineStr"/>
+      <c r="EA168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -40331,7 +40503,7 @@
       <c r="N169" t="n">
         <v>96</v>
       </c>
-      <c r="O169" t="b">
+      <c r="O169" t="n">
         <v>0</v>
       </c>
       <c r="P169" t="n">
@@ -40513,6 +40685,7 @@
       <c r="DX169" t="inlineStr"/>
       <c r="DY169" t="inlineStr"/>
       <c r="DZ169" t="inlineStr"/>
+      <c r="EA169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -40566,7 +40739,7 @@
       <c r="N170" t="n">
         <v>228</v>
       </c>
-      <c r="O170" t="b">
+      <c r="O170" t="n">
         <v>0</v>
       </c>
       <c r="P170" t="n">
@@ -40748,6 +40921,7 @@
       <c r="DX170" t="inlineStr"/>
       <c r="DY170" t="inlineStr"/>
       <c r="DZ170" t="inlineStr"/>
+      <c r="EA170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -40801,7 +40975,7 @@
       <c r="N171" t="n">
         <v>228</v>
       </c>
-      <c r="O171" t="b">
+      <c r="O171" t="n">
         <v>0</v>
       </c>
       <c r="P171" t="n">
@@ -40983,6 +41157,7 @@
       <c r="DX171" t="inlineStr"/>
       <c r="DY171" t="inlineStr"/>
       <c r="DZ171" t="inlineStr"/>
+      <c r="EA171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -41038,7 +41213,7 @@
       <c r="N172" t="n">
         <v>228</v>
       </c>
-      <c r="O172" t="b">
+      <c r="O172" t="n">
         <v>0</v>
       </c>
       <c r="P172" t="n">
@@ -41220,6 +41395,7 @@
       <c r="DX172" t="inlineStr"/>
       <c r="DY172" t="inlineStr"/>
       <c r="DZ172" t="inlineStr"/>
+      <c r="EA172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -41273,7 +41449,7 @@
       <c r="N173" t="n">
         <v>228</v>
       </c>
-      <c r="O173" t="b">
+      <c r="O173" t="n">
         <v>0</v>
       </c>
       <c r="P173" t="n">
@@ -41455,6 +41631,7 @@
       <c r="DX173" t="inlineStr"/>
       <c r="DY173" t="inlineStr"/>
       <c r="DZ173" t="inlineStr"/>
+      <c r="EA173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -41508,7 +41685,7 @@
       <c r="N174" t="n">
         <v>8</v>
       </c>
-      <c r="O174" t="b">
+      <c r="O174" t="n">
         <v>0</v>
       </c>
       <c r="P174" t="n">
@@ -41690,6 +41867,7 @@
       <c r="DX174" t="inlineStr"/>
       <c r="DY174" t="inlineStr"/>
       <c r="DZ174" t="inlineStr"/>
+      <c r="EA174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -41743,7 +41921,7 @@
       <c r="N175" t="n">
         <v>7</v>
       </c>
-      <c r="O175" t="b">
+      <c r="O175" t="n">
         <v>0</v>
       </c>
       <c r="P175" t="n">
@@ -41925,6 +42103,7 @@
       <c r="DX175" t="inlineStr"/>
       <c r="DY175" t="inlineStr"/>
       <c r="DZ175" t="inlineStr"/>
+      <c r="EA175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -41978,7 +42157,7 @@
       <c r="N176" t="n">
         <v>7</v>
       </c>
-      <c r="O176" t="b">
+      <c r="O176" t="n">
         <v>0</v>
       </c>
       <c r="P176" t="n">
@@ -42160,6 +42339,7 @@
       <c r="DX176" t="inlineStr"/>
       <c r="DY176" t="inlineStr"/>
       <c r="DZ176" t="inlineStr"/>
+      <c r="EA176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -42213,7 +42393,7 @@
       <c r="N177" t="n">
         <v>7</v>
       </c>
-      <c r="O177" t="b">
+      <c r="O177" t="n">
         <v>0</v>
       </c>
       <c r="P177" t="n">
@@ -42395,6 +42575,7 @@
       <c r="DX177" t="inlineStr"/>
       <c r="DY177" t="inlineStr"/>
       <c r="DZ177" t="inlineStr"/>
+      <c r="EA177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -42448,7 +42629,7 @@
       <c r="N178" t="n">
         <v>7</v>
       </c>
-      <c r="O178" t="b">
+      <c r="O178" t="n">
         <v>0</v>
       </c>
       <c r="P178" t="n">
@@ -42630,6 +42811,7 @@
       <c r="DX178" t="inlineStr"/>
       <c r="DY178" t="inlineStr"/>
       <c r="DZ178" t="inlineStr"/>
+      <c r="EA178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -42683,7 +42865,7 @@
       <c r="N179" t="n">
         <v>9</v>
       </c>
-      <c r="O179" t="b">
+      <c r="O179" t="n">
         <v>0</v>
       </c>
       <c r="P179" t="n">
@@ -42865,6 +43047,7 @@
       <c r="DX179" t="inlineStr"/>
       <c r="DY179" t="inlineStr"/>
       <c r="DZ179" t="inlineStr"/>
+      <c r="EA179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -42918,7 +43101,7 @@
       <c r="N180" t="n">
         <v>9</v>
       </c>
-      <c r="O180" t="b">
+      <c r="O180" t="n">
         <v>0</v>
       </c>
       <c r="P180" t="n">
@@ -43100,6 +43283,7 @@
       <c r="DX180" t="inlineStr"/>
       <c r="DY180" t="inlineStr"/>
       <c r="DZ180" t="inlineStr"/>
+      <c r="EA180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -43153,7 +43337,7 @@
       <c r="N181" t="n">
         <v>9</v>
       </c>
-      <c r="O181" t="b">
+      <c r="O181" t="n">
         <v>0</v>
       </c>
       <c r="P181" t="n">
@@ -43335,6 +43519,7 @@
       <c r="DX181" t="inlineStr"/>
       <c r="DY181" t="inlineStr"/>
       <c r="DZ181" t="inlineStr"/>
+      <c r="EA181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -43388,7 +43573,7 @@
       <c r="N182" t="n">
         <v>11</v>
       </c>
-      <c r="O182" t="b">
+      <c r="O182" t="n">
         <v>0</v>
       </c>
       <c r="P182" t="n">
@@ -43570,6 +43755,7 @@
       <c r="DX182" t="inlineStr"/>
       <c r="DY182" t="inlineStr"/>
       <c r="DZ182" t="inlineStr"/>
+      <c r="EA182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -43623,7 +43809,7 @@
       <c r="N183" t="n">
         <v>11</v>
       </c>
-      <c r="O183" t="b">
+      <c r="O183" t="n">
         <v>0</v>
       </c>
       <c r="P183" t="n">
@@ -43805,6 +43991,7 @@
       <c r="DX183" t="inlineStr"/>
       <c r="DY183" t="inlineStr"/>
       <c r="DZ183" t="inlineStr"/>
+      <c r="EA183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -43858,7 +44045,7 @@
       <c r="N184" t="n">
         <v>11</v>
       </c>
-      <c r="O184" t="b">
+      <c r="O184" t="n">
         <v>0</v>
       </c>
       <c r="P184" t="n">
@@ -44040,6 +44227,7 @@
       <c r="DX184" t="inlineStr"/>
       <c r="DY184" t="inlineStr"/>
       <c r="DZ184" t="inlineStr"/>
+      <c r="EA184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -44093,7 +44281,7 @@
       <c r="N185" t="n">
         <v>11</v>
       </c>
-      <c r="O185" t="b">
+      <c r="O185" t="n">
         <v>0</v>
       </c>
       <c r="P185" t="n">
@@ -44275,6 +44463,7 @@
       <c r="DX185" t="inlineStr"/>
       <c r="DY185" t="inlineStr"/>
       <c r="DZ185" t="inlineStr"/>
+      <c r="EA185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -44328,7 +44517,7 @@
       <c r="N186" t="n">
         <v>9</v>
       </c>
-      <c r="O186" t="b">
+      <c r="O186" t="n">
         <v>0</v>
       </c>
       <c r="P186" t="n">
@@ -44510,6 +44699,7 @@
       <c r="DX186" t="inlineStr"/>
       <c r="DY186" t="inlineStr"/>
       <c r="DZ186" t="inlineStr"/>
+      <c r="EA186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -44563,7 +44753,7 @@
       <c r="N187" t="n">
         <v>9</v>
       </c>
-      <c r="O187" t="b">
+      <c r="O187" t="n">
         <v>0</v>
       </c>
       <c r="P187" t="n">
@@ -44745,6 +44935,7 @@
       <c r="DX187" t="inlineStr"/>
       <c r="DY187" t="inlineStr"/>
       <c r="DZ187" t="inlineStr"/>
+      <c r="EA187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -44798,7 +44989,7 @@
       <c r="N188" t="n">
         <v>9</v>
       </c>
-      <c r="O188" t="b">
+      <c r="O188" t="n">
         <v>0</v>
       </c>
       <c r="P188" t="n">
@@ -44980,6 +45171,7 @@
       <c r="DX188" t="inlineStr"/>
       <c r="DY188" t="inlineStr"/>
       <c r="DZ188" t="inlineStr"/>
+      <c r="EA188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -45033,7 +45225,7 @@
       <c r="N189" t="n">
         <v>9</v>
       </c>
-      <c r="O189" t="b">
+      <c r="O189" t="n">
         <v>0</v>
       </c>
       <c r="P189" t="n">
@@ -45215,6 +45407,7 @@
       <c r="DX189" t="inlineStr"/>
       <c r="DY189" t="inlineStr"/>
       <c r="DZ189" t="inlineStr"/>
+      <c r="EA189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -45268,7 +45461,7 @@
       <c r="N190" t="n">
         <v>9</v>
       </c>
-      <c r="O190" t="b">
+      <c r="O190" t="n">
         <v>0</v>
       </c>
       <c r="P190" t="n">
@@ -45450,6 +45643,7 @@
       <c r="DX190" t="inlineStr"/>
       <c r="DY190" t="inlineStr"/>
       <c r="DZ190" t="inlineStr"/>
+      <c r="EA190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -45503,7 +45697,7 @@
       <c r="N191" t="n">
         <v>9</v>
       </c>
-      <c r="O191" t="b">
+      <c r="O191" t="n">
         <v>0</v>
       </c>
       <c r="P191" t="n">
@@ -45685,6 +45879,7 @@
       <c r="DX191" t="inlineStr"/>
       <c r="DY191" t="inlineStr"/>
       <c r="DZ191" t="inlineStr"/>
+      <c r="EA191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -45738,7 +45933,7 @@
       <c r="N192" t="n">
         <v>9</v>
       </c>
-      <c r="O192" t="b">
+      <c r="O192" t="n">
         <v>0</v>
       </c>
       <c r="P192" t="n">
@@ -45920,6 +46115,7 @@
       <c r="DX192" t="inlineStr"/>
       <c r="DY192" t="inlineStr"/>
       <c r="DZ192" t="inlineStr"/>
+      <c r="EA192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -45973,7 +46169,7 @@
       <c r="N193" t="n">
         <v>9</v>
       </c>
-      <c r="O193" t="b">
+      <c r="O193" t="n">
         <v>0</v>
       </c>
       <c r="P193" t="n">
@@ -46155,6 +46351,7 @@
       <c r="DX193" t="inlineStr"/>
       <c r="DY193" t="inlineStr"/>
       <c r="DZ193" t="inlineStr"/>
+      <c r="EA193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -46208,7 +46405,7 @@
       <c r="N194" t="n">
         <v>9</v>
       </c>
-      <c r="O194" t="b">
+      <c r="O194" t="n">
         <v>0</v>
       </c>
       <c r="P194" t="n">
@@ -46390,6 +46587,7 @@
       <c r="DX194" t="inlineStr"/>
       <c r="DY194" t="inlineStr"/>
       <c r="DZ194" t="inlineStr"/>
+      <c r="EA194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -46443,7 +46641,7 @@
       <c r="N195" t="n">
         <v>9</v>
       </c>
-      <c r="O195" t="b">
+      <c r="O195" t="n">
         <v>0</v>
       </c>
       <c r="P195" t="n">
@@ -46625,6 +46823,7 @@
       <c r="DX195" t="inlineStr"/>
       <c r="DY195" t="inlineStr"/>
       <c r="DZ195" t="inlineStr"/>
+      <c r="EA195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -46678,7 +46877,7 @@
       <c r="N196" t="n">
         <v>9</v>
       </c>
-      <c r="O196" t="b">
+      <c r="O196" t="n">
         <v>0</v>
       </c>
       <c r="P196" t="n">
@@ -46860,6 +47059,7 @@
       <c r="DX196" t="inlineStr"/>
       <c r="DY196" t="inlineStr"/>
       <c r="DZ196" t="inlineStr"/>
+      <c r="EA196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -46912,7 +47112,7 @@
       <c r="N197" t="n">
         <v>95</v>
       </c>
-      <c r="O197" t="b">
+      <c r="O197" t="n">
         <v>0</v>
       </c>
       <c r="P197" t="n">
@@ -47094,6 +47294,7 @@
       <c r="DX197" t="inlineStr"/>
       <c r="DY197" t="inlineStr"/>
       <c r="DZ197" t="inlineStr"/>
+      <c r="EA197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -47147,7 +47348,7 @@
       <c r="N198" t="n">
         <v>95</v>
       </c>
-      <c r="O198" t="b">
+      <c r="O198" t="n">
         <v>0</v>
       </c>
       <c r="P198" t="n">
@@ -47329,6 +47530,7 @@
       <c r="DX198" t="inlineStr"/>
       <c r="DY198" t="inlineStr"/>
       <c r="DZ198" t="inlineStr"/>
+      <c r="EA198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -47383,7 +47585,7 @@
       <c r="N199" t="n">
         <v>95</v>
       </c>
-      <c r="O199" t="b">
+      <c r="O199" t="n">
         <v>0</v>
       </c>
       <c r="P199" t="n">
@@ -47565,6 +47767,7 @@
       <c r="DX199" t="inlineStr"/>
       <c r="DY199" t="inlineStr"/>
       <c r="DZ199" t="inlineStr"/>
+      <c r="EA199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -47618,7 +47821,7 @@
       <c r="N200" t="n">
         <v>95</v>
       </c>
-      <c r="O200" t="b">
+      <c r="O200" t="n">
         <v>0</v>
       </c>
       <c r="P200" t="n">
@@ -47800,6 +48003,7 @@
       <c r="DX200" t="inlineStr"/>
       <c r="DY200" t="inlineStr"/>
       <c r="DZ200" t="inlineStr"/>
+      <c r="EA200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -47853,7 +48057,7 @@
       <c r="N201" t="n">
         <v>95</v>
       </c>
-      <c r="O201" t="b">
+      <c r="O201" t="n">
         <v>0</v>
       </c>
       <c r="P201" t="n">
@@ -48035,6 +48239,7 @@
       <c r="DX201" t="inlineStr"/>
       <c r="DY201" t="inlineStr"/>
       <c r="DZ201" t="inlineStr"/>
+      <c r="EA201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -48088,7 +48293,7 @@
       <c r="N202" t="n">
         <v>95</v>
       </c>
-      <c r="O202" t="b">
+      <c r="O202" t="n">
         <v>0</v>
       </c>
       <c r="P202" t="n">
@@ -48270,6 +48475,7 @@
       <c r="DX202" t="inlineStr"/>
       <c r="DY202" t="inlineStr"/>
       <c r="DZ202" t="inlineStr"/>
+      <c r="EA202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -48323,7 +48529,7 @@
       <c r="N203" t="n">
         <v>95</v>
       </c>
-      <c r="O203" t="b">
+      <c r="O203" t="n">
         <v>0</v>
       </c>
       <c r="P203" t="n">
@@ -48505,6 +48711,7 @@
       <c r="DX203" t="inlineStr"/>
       <c r="DY203" t="inlineStr"/>
       <c r="DZ203" t="inlineStr"/>
+      <c r="EA203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -48558,7 +48765,7 @@
       <c r="N204" t="n">
         <v>228</v>
       </c>
-      <c r="O204" t="b">
+      <c r="O204" t="n">
         <v>0</v>
       </c>
       <c r="P204" t="n">
@@ -48740,6 +48947,7 @@
       <c r="DX204" t="inlineStr"/>
       <c r="DY204" t="inlineStr"/>
       <c r="DZ204" t="inlineStr"/>
+      <c r="EA204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -48793,7 +49001,7 @@
       <c r="N205" t="n">
         <v>228</v>
       </c>
-      <c r="O205" t="b">
+      <c r="O205" t="n">
         <v>0</v>
       </c>
       <c r="P205" t="n">
@@ -48975,6 +49183,7 @@
       <c r="DX205" t="inlineStr"/>
       <c r="DY205" t="inlineStr"/>
       <c r="DZ205" t="inlineStr"/>
+      <c r="EA205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -49028,7 +49237,7 @@
       <c r="N206" t="n">
         <v>228</v>
       </c>
-      <c r="O206" t="b">
+      <c r="O206" t="n">
         <v>0</v>
       </c>
       <c r="P206" t="n">
@@ -49210,6 +49419,7 @@
       <c r="DX206" t="inlineStr"/>
       <c r="DY206" t="inlineStr"/>
       <c r="DZ206" t="inlineStr"/>
+      <c r="EA206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -49263,7 +49473,7 @@
       <c r="N207" t="n">
         <v>228</v>
       </c>
-      <c r="O207" t="b">
+      <c r="O207" t="n">
         <v>0</v>
       </c>
       <c r="P207" t="n">
@@ -49445,6 +49655,7 @@
       <c r="DX207" t="inlineStr"/>
       <c r="DY207" t="inlineStr"/>
       <c r="DZ207" t="inlineStr"/>
+      <c r="EA207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -49498,7 +49709,7 @@
       <c r="N208" t="n">
         <v>228</v>
       </c>
-      <c r="O208" t="b">
+      <c r="O208" t="n">
         <v>0</v>
       </c>
       <c r="P208" t="n">
@@ -49680,6 +49891,7 @@
       <c r="DX208" t="inlineStr"/>
       <c r="DY208" t="inlineStr"/>
       <c r="DZ208" t="inlineStr"/>
+      <c r="EA208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -49733,7 +49945,7 @@
       <c r="N209" t="n">
         <v>228</v>
       </c>
-      <c r="O209" t="b">
+      <c r="O209" t="n">
         <v>0</v>
       </c>
       <c r="P209" t="n">
@@ -49915,6 +50127,7 @@
       <c r="DX209" t="inlineStr"/>
       <c r="DY209" t="inlineStr"/>
       <c r="DZ209" t="inlineStr"/>
+      <c r="EA209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -49968,7 +50181,7 @@
       <c r="N210" t="n">
         <v>228</v>
       </c>
-      <c r="O210" t="b">
+      <c r="O210" t="n">
         <v>0</v>
       </c>
       <c r="P210" t="n">
@@ -50150,6 +50363,7 @@
       <c r="DX210" t="inlineStr"/>
       <c r="DY210" t="inlineStr"/>
       <c r="DZ210" t="inlineStr"/>
+      <c r="EA210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -50203,7 +50417,7 @@
       <c r="N211" t="n">
         <v>228</v>
       </c>
-      <c r="O211" t="b">
+      <c r="O211" t="n">
         <v>0</v>
       </c>
       <c r="P211" t="n">
@@ -50385,6 +50599,7 @@
       <c r="DX211" t="inlineStr"/>
       <c r="DY211" t="inlineStr"/>
       <c r="DZ211" t="inlineStr"/>
+      <c r="EA211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -50438,7 +50653,7 @@
       <c r="N212" t="n">
         <v>228</v>
       </c>
-      <c r="O212" t="b">
+      <c r="O212" t="n">
         <v>0</v>
       </c>
       <c r="P212" t="n">
@@ -50620,6 +50835,7 @@
       <c r="DX212" t="inlineStr"/>
       <c r="DY212" t="inlineStr"/>
       <c r="DZ212" t="inlineStr"/>
+      <c r="EA212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -50673,7 +50889,7 @@
       <c r="N213" t="n">
         <v>228</v>
       </c>
-      <c r="O213" t="b">
+      <c r="O213" t="n">
         <v>0</v>
       </c>
       <c r="P213" t="n">
@@ -50855,6 +51071,7 @@
       <c r="DX213" t="inlineStr"/>
       <c r="DY213" t="inlineStr"/>
       <c r="DZ213" t="inlineStr"/>
+      <c r="EA213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -50908,7 +51125,7 @@
       <c r="N214" t="n">
         <v>228</v>
       </c>
-      <c r="O214" t="b">
+      <c r="O214" t="n">
         <v>0</v>
       </c>
       <c r="P214" t="n">
@@ -51090,6 +51307,7 @@
       <c r="DX214" t="inlineStr"/>
       <c r="DY214" t="inlineStr"/>
       <c r="DZ214" t="inlineStr"/>
+      <c r="EA214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -51143,7 +51361,7 @@
       <c r="N215" t="n">
         <v>228</v>
       </c>
-      <c r="O215" t="b">
+      <c r="O215" t="n">
         <v>0</v>
       </c>
       <c r="P215" t="n">
@@ -51325,6 +51543,7 @@
       <c r="DX215" t="inlineStr"/>
       <c r="DY215" t="inlineStr"/>
       <c r="DZ215" t="inlineStr"/>
+      <c r="EA215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -51378,7 +51597,7 @@
       <c r="N216" t="n">
         <v>228</v>
       </c>
-      <c r="O216" t="b">
+      <c r="O216" t="n">
         <v>0</v>
       </c>
       <c r="P216" t="n">
@@ -51560,6 +51779,7 @@
       <c r="DX216" t="inlineStr"/>
       <c r="DY216" t="inlineStr"/>
       <c r="DZ216" t="inlineStr"/>
+      <c r="EA216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -51613,7 +51833,7 @@
       <c r="N217" t="n">
         <v>228</v>
       </c>
-      <c r="O217" t="b">
+      <c r="O217" t="n">
         <v>0</v>
       </c>
       <c r="P217" t="n">
@@ -51795,6 +52015,7 @@
       <c r="DX217" t="inlineStr"/>
       <c r="DY217" t="inlineStr"/>
       <c r="DZ217" t="inlineStr"/>
+      <c r="EA217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -51850,7 +52071,7 @@
       <c r="N218" t="n">
         <v>228</v>
       </c>
-      <c r="O218" t="b">
+      <c r="O218" t="n">
         <v>0</v>
       </c>
       <c r="P218" t="n">
@@ -52032,6 +52253,7 @@
       <c r="DX218" t="inlineStr"/>
       <c r="DY218" t="inlineStr"/>
       <c r="DZ218" t="inlineStr"/>
+      <c r="EA218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -52087,7 +52309,7 @@
       <c r="N219" t="n">
         <v>228</v>
       </c>
-      <c r="O219" t="b">
+      <c r="O219" t="n">
         <v>0</v>
       </c>
       <c r="P219" t="n">
@@ -52269,6 +52491,7 @@
       <c r="DX219" t="inlineStr"/>
       <c r="DY219" t="inlineStr"/>
       <c r="DZ219" t="inlineStr"/>
+      <c r="EA219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -52324,7 +52547,7 @@
       <c r="N220" t="n">
         <v>228</v>
       </c>
-      <c r="O220" t="b">
+      <c r="O220" t="n">
         <v>0</v>
       </c>
       <c r="P220" t="n">
@@ -52506,6 +52729,7 @@
       <c r="DX220" t="inlineStr"/>
       <c r="DY220" t="inlineStr"/>
       <c r="DZ220" t="inlineStr"/>
+      <c r="EA220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -52561,7 +52785,7 @@
       <c r="N221" t="n">
         <v>228</v>
       </c>
-      <c r="O221" t="b">
+      <c r="O221" t="n">
         <v>0</v>
       </c>
       <c r="P221" t="n">
@@ -52743,6 +52967,7 @@
       <c r="DX221" t="inlineStr"/>
       <c r="DY221" t="inlineStr"/>
       <c r="DZ221" t="inlineStr"/>
+      <c r="EA221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -52796,7 +53021,7 @@
       <c r="N222" t="n">
         <v>228</v>
       </c>
-      <c r="O222" t="b">
+      <c r="O222" t="n">
         <v>0</v>
       </c>
       <c r="P222" t="n">
@@ -52978,6 +53203,7 @@
       <c r="DX222" t="inlineStr"/>
       <c r="DY222" t="inlineStr"/>
       <c r="DZ222" t="inlineStr"/>
+      <c r="EA222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -53031,7 +53257,7 @@
       <c r="N223" t="n">
         <v>228</v>
       </c>
-      <c r="O223" t="b">
+      <c r="O223" t="n">
         <v>0</v>
       </c>
       <c r="P223" t="n">
@@ -53213,6 +53439,7 @@
       <c r="DX223" t="inlineStr"/>
       <c r="DY223" t="inlineStr"/>
       <c r="DZ223" t="inlineStr"/>
+      <c r="EA223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -53266,7 +53493,7 @@
       <c r="N224" t="n">
         <v>228</v>
       </c>
-      <c r="O224" t="b">
+      <c r="O224" t="n">
         <v>0</v>
       </c>
       <c r="P224" t="n">
@@ -53448,6 +53675,7 @@
       <c r="DX224" t="inlineStr"/>
       <c r="DY224" t="inlineStr"/>
       <c r="DZ224" t="inlineStr"/>
+      <c r="EA224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -53501,7 +53729,7 @@
       <c r="N225" t="n">
         <v>228</v>
       </c>
-      <c r="O225" t="b">
+      <c r="O225" t="n">
         <v>0</v>
       </c>
       <c r="P225" t="n">
@@ -53683,6 +53911,7 @@
       <c r="DX225" t="inlineStr"/>
       <c r="DY225" t="inlineStr"/>
       <c r="DZ225" t="inlineStr"/>
+      <c r="EA225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -53736,7 +53965,7 @@
       <c r="N226" t="n">
         <v>228</v>
       </c>
-      <c r="O226" t="b">
+      <c r="O226" t="n">
         <v>0</v>
       </c>
       <c r="P226" t="n">
@@ -53918,6 +54147,7 @@
       <c r="DX226" t="inlineStr"/>
       <c r="DY226" t="inlineStr"/>
       <c r="DZ226" t="inlineStr"/>
+      <c r="EA226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -53971,7 +54201,7 @@
       <c r="N227" t="n">
         <v>28</v>
       </c>
-      <c r="O227" t="b">
+      <c r="O227" t="n">
         <v>0</v>
       </c>
       <c r="P227" t="n">
@@ -54153,6 +54383,7 @@
       <c r="DX227" t="inlineStr"/>
       <c r="DY227" t="inlineStr"/>
       <c r="DZ227" t="inlineStr"/>
+      <c r="EA227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -54206,7 +54437,7 @@
       <c r="N228" t="n">
         <v>28</v>
       </c>
-      <c r="O228" t="b">
+      <c r="O228" t="n">
         <v>0</v>
       </c>
       <c r="P228" t="n">
@@ -54388,6 +54619,7 @@
       <c r="DX228" t="inlineStr"/>
       <c r="DY228" t="inlineStr"/>
       <c r="DZ228" t="inlineStr"/>
+      <c r="EA228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -54443,7 +54675,7 @@
       <c r="N229" t="n">
         <v>28</v>
       </c>
-      <c r="O229" t="b">
+      <c r="O229" t="n">
         <v>0</v>
       </c>
       <c r="P229" t="n">
@@ -54625,6 +54857,7 @@
       <c r="DX229" t="inlineStr"/>
       <c r="DY229" t="inlineStr"/>
       <c r="DZ229" t="inlineStr"/>
+      <c r="EA229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -54678,7 +54911,7 @@
       <c r="N230" t="n">
         <v>28</v>
       </c>
-      <c r="O230" t="b">
+      <c r="O230" t="n">
         <v>0</v>
       </c>
       <c r="P230" t="n">
@@ -54860,6 +55093,7 @@
       <c r="DX230" t="inlineStr"/>
       <c r="DY230" t="inlineStr"/>
       <c r="DZ230" t="inlineStr"/>
+      <c r="EA230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -54913,7 +55147,7 @@
       <c r="N231" t="n">
         <v>28</v>
       </c>
-      <c r="O231" t="b">
+      <c r="O231" t="n">
         <v>0</v>
       </c>
       <c r="P231" t="n">
@@ -55095,6 +55329,7 @@
       <c r="DX231" t="inlineStr"/>
       <c r="DY231" t="inlineStr"/>
       <c r="DZ231" t="inlineStr"/>
+      <c r="EA231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -55148,7 +55383,7 @@
       <c r="N232" t="n">
         <v>28</v>
       </c>
-      <c r="O232" t="b">
+      <c r="O232" t="n">
         <v>0</v>
       </c>
       <c r="P232" t="n">
@@ -55330,6 +55565,7 @@
       <c r="DX232" t="inlineStr"/>
       <c r="DY232" t="inlineStr"/>
       <c r="DZ232" t="inlineStr"/>
+      <c r="EA232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -55383,7 +55619,7 @@
       <c r="N233" t="n">
         <v>28</v>
       </c>
-      <c r="O233" t="b">
+      <c r="O233" t="n">
         <v>0</v>
       </c>
       <c r="P233" t="n">
@@ -55565,6 +55801,7 @@
       <c r="DX233" t="inlineStr"/>
       <c r="DY233" t="inlineStr"/>
       <c r="DZ233" t="inlineStr"/>
+      <c r="EA233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -55618,7 +55855,7 @@
       <c r="N234" t="n">
         <v>28</v>
       </c>
-      <c r="O234" t="b">
+      <c r="O234" t="n">
         <v>0</v>
       </c>
       <c r="P234" t="n">
@@ -55800,6 +56037,7 @@
       <c r="DX234" t="inlineStr"/>
       <c r="DY234" t="inlineStr"/>
       <c r="DZ234" t="inlineStr"/>
+      <c r="EA234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -55853,7 +56091,7 @@
       <c r="N235" t="n">
         <v>28</v>
       </c>
-      <c r="O235" t="b">
+      <c r="O235" t="n">
         <v>0</v>
       </c>
       <c r="P235" t="n">
@@ -56035,6 +56273,7 @@
       <c r="DX235" t="inlineStr"/>
       <c r="DY235" t="inlineStr"/>
       <c r="DZ235" t="inlineStr"/>
+      <c r="EA235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -56088,7 +56327,7 @@
       <c r="N236" t="n">
         <v>28</v>
       </c>
-      <c r="O236" t="b">
+      <c r="O236" t="n">
         <v>0</v>
       </c>
       <c r="P236" t="n">
@@ -56270,6 +56509,7 @@
       <c r="DX236" t="inlineStr"/>
       <c r="DY236" t="inlineStr"/>
       <c r="DZ236" t="inlineStr"/>
+      <c r="EA236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -56323,7 +56563,7 @@
       <c r="N237" t="n">
         <v>28</v>
       </c>
-      <c r="O237" t="b">
+      <c r="O237" t="n">
         <v>0</v>
       </c>
       <c r="P237" t="n">
@@ -56505,6 +56745,7 @@
       <c r="DX237" t="inlineStr"/>
       <c r="DY237" t="inlineStr"/>
       <c r="DZ237" t="inlineStr"/>
+      <c r="EA237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -56558,7 +56799,7 @@
       <c r="N238" t="n">
         <v>28</v>
       </c>
-      <c r="O238" t="b">
+      <c r="O238" t="n">
         <v>0</v>
       </c>
       <c r="P238" t="n">
@@ -56740,6 +56981,7 @@
       <c r="DX238" t="inlineStr"/>
       <c r="DY238" t="inlineStr"/>
       <c r="DZ238" t="inlineStr"/>
+      <c r="EA238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -56793,7 +57035,7 @@
       <c r="N239" t="n">
         <v>28</v>
       </c>
-      <c r="O239" t="b">
+      <c r="O239" t="n">
         <v>0</v>
       </c>
       <c r="P239" t="n">
@@ -56975,6 +57217,7 @@
       <c r="DX239" t="inlineStr"/>
       <c r="DY239" t="inlineStr"/>
       <c r="DZ239" t="inlineStr"/>
+      <c r="EA239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -57028,7 +57271,7 @@
       <c r="N240" t="n">
         <v>228</v>
       </c>
-      <c r="O240" t="b">
+      <c r="O240" t="n">
         <v>0</v>
       </c>
       <c r="P240" t="n">
@@ -57210,6 +57453,7 @@
       <c r="DX240" t="inlineStr"/>
       <c r="DY240" t="inlineStr"/>
       <c r="DZ240" t="inlineStr"/>
+      <c r="EA240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -57263,7 +57507,7 @@
       <c r="N241" t="n">
         <v>268</v>
       </c>
-      <c r="O241" t="b">
+      <c r="O241" t="n">
         <v>0</v>
       </c>
       <c r="P241" t="n">
@@ -57445,6 +57689,7 @@
       <c r="DX241" t="inlineStr"/>
       <c r="DY241" t="inlineStr"/>
       <c r="DZ241" t="inlineStr"/>
+      <c r="EA241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -57498,7 +57743,7 @@
       <c r="N242" t="n">
         <v>268</v>
       </c>
-      <c r="O242" t="b">
+      <c r="O242" t="n">
         <v>0</v>
       </c>
       <c r="P242" t="n">
@@ -57680,6 +57925,7 @@
       <c r="DX242" t="inlineStr"/>
       <c r="DY242" t="inlineStr"/>
       <c r="DZ242" t="inlineStr"/>
+      <c r="EA242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -57733,7 +57979,7 @@
       <c r="N243" t="n">
         <v>68</v>
       </c>
-      <c r="O243" t="b">
+      <c r="O243" t="n">
         <v>0</v>
       </c>
       <c r="P243" t="n">
@@ -57915,6 +58161,7 @@
       <c r="DX243" t="inlineStr"/>
       <c r="DY243" t="inlineStr"/>
       <c r="DZ243" t="inlineStr"/>
+      <c r="EA243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -57968,7 +58215,7 @@
       <c r="N244" t="n">
         <v>68</v>
       </c>
-      <c r="O244" t="b">
+      <c r="O244" t="n">
         <v>0</v>
       </c>
       <c r="P244" t="n">
@@ -58150,6 +58397,7 @@
       <c r="DX244" t="inlineStr"/>
       <c r="DY244" t="inlineStr"/>
       <c r="DZ244" t="inlineStr"/>
+      <c r="EA244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -58203,7 +58451,7 @@
       <c r="N245" t="n">
         <v>68</v>
       </c>
-      <c r="O245" t="b">
+      <c r="O245" t="n">
         <v>0</v>
       </c>
       <c r="P245" t="n">
@@ -58385,6 +58633,7 @@
       <c r="DX245" t="inlineStr"/>
       <c r="DY245" t="inlineStr"/>
       <c r="DZ245" t="inlineStr"/>
+      <c r="EA245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -58438,7 +58687,7 @@
       <c r="N246" t="n">
         <v>68</v>
       </c>
-      <c r="O246" t="b">
+      <c r="O246" t="n">
         <v>0</v>
       </c>
       <c r="P246" t="n">
@@ -58620,6 +58869,7 @@
       <c r="DX246" t="inlineStr"/>
       <c r="DY246" t="inlineStr"/>
       <c r="DZ246" t="inlineStr"/>
+      <c r="EA246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -58673,7 +58923,7 @@
       <c r="N247" t="n">
         <v>68</v>
       </c>
-      <c r="O247" t="b">
+      <c r="O247" t="n">
         <v>0</v>
       </c>
       <c r="P247" t="n">
@@ -58855,6 +59105,7 @@
       <c r="DX247" t="inlineStr"/>
       <c r="DY247" t="inlineStr"/>
       <c r="DZ247" t="inlineStr"/>
+      <c r="EA247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -58908,7 +59159,7 @@
       <c r="N248" t="n">
         <v>68</v>
       </c>
-      <c r="O248" t="b">
+      <c r="O248" t="n">
         <v>0</v>
       </c>
       <c r="P248" t="n">
@@ -59090,6 +59341,7 @@
       <c r="DX248" t="inlineStr"/>
       <c r="DY248" t="inlineStr"/>
       <c r="DZ248" t="inlineStr"/>
+      <c r="EA248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -59143,7 +59395,7 @@
       <c r="N249" t="n">
         <v>68</v>
       </c>
-      <c r="O249" t="b">
+      <c r="O249" t="n">
         <v>0</v>
       </c>
       <c r="P249" t="n">
@@ -59325,6 +59577,7 @@
       <c r="DX249" t="inlineStr"/>
       <c r="DY249" t="inlineStr"/>
       <c r="DZ249" t="inlineStr"/>
+      <c r="EA249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -59379,7 +59632,7 @@
       <c r="N250" t="n">
         <v>68</v>
       </c>
-      <c r="O250" t="b">
+      <c r="O250" t="n">
         <v>0</v>
       </c>
       <c r="P250" t="n">
@@ -59561,6 +59814,7 @@
       <c r="DX250" t="inlineStr"/>
       <c r="DY250" t="inlineStr"/>
       <c r="DZ250" t="inlineStr"/>
+      <c r="EA250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -59615,7 +59869,7 @@
       <c r="N251" t="n">
         <v>68</v>
       </c>
-      <c r="O251" t="b">
+      <c r="O251" t="n">
         <v>0</v>
       </c>
       <c r="P251" t="n">
@@ -59797,6 +60051,7 @@
       <c r="DX251" t="inlineStr"/>
       <c r="DY251" t="inlineStr"/>
       <c r="DZ251" t="inlineStr"/>
+      <c r="EA251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -59851,7 +60106,7 @@
       <c r="N252" t="n">
         <v>68</v>
       </c>
-      <c r="O252" t="b">
+      <c r="O252" t="n">
         <v>0</v>
       </c>
       <c r="P252" t="n">
@@ -60033,6 +60288,7 @@
       <c r="DX252" t="inlineStr"/>
       <c r="DY252" t="inlineStr"/>
       <c r="DZ252" t="inlineStr"/>
+      <c r="EA252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -60086,7 +60342,7 @@
       <c r="N253" t="n">
         <v>68</v>
       </c>
-      <c r="O253" t="b">
+      <c r="O253" t="n">
         <v>0</v>
       </c>
       <c r="P253" t="n">
@@ -60268,6 +60524,7 @@
       <c r="DX253" t="inlineStr"/>
       <c r="DY253" t="inlineStr"/>
       <c r="DZ253" t="inlineStr"/>
+      <c r="EA253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -60321,7 +60578,7 @@
       <c r="N254" t="n">
         <v>68</v>
       </c>
-      <c r="O254" t="b">
+      <c r="O254" t="n">
         <v>0</v>
       </c>
       <c r="P254" t="n">
@@ -60503,6 +60760,7 @@
       <c r="DX254" t="inlineStr"/>
       <c r="DY254" t="inlineStr"/>
       <c r="DZ254" t="inlineStr"/>
+      <c r="EA254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -60556,7 +60814,7 @@
       <c r="N255" t="n">
         <v>68</v>
       </c>
-      <c r="O255" t="b">
+      <c r="O255" t="n">
         <v>0</v>
       </c>
       <c r="P255" t="n">
@@ -60738,6 +60996,7 @@
       <c r="DX255" t="inlineStr"/>
       <c r="DY255" t="inlineStr"/>
       <c r="DZ255" t="inlineStr"/>
+      <c r="EA255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -60791,7 +61050,7 @@
       <c r="N256" t="n">
         <v>68</v>
       </c>
-      <c r="O256" t="b">
+      <c r="O256" t="n">
         <v>0</v>
       </c>
       <c r="P256" t="n">
@@ -60973,6 +61232,7 @@
       <c r="DX256" t="inlineStr"/>
       <c r="DY256" t="inlineStr"/>
       <c r="DZ256" t="inlineStr"/>
+      <c r="EA256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -61026,7 +61286,7 @@
       <c r="N257" t="n">
         <v>68</v>
       </c>
-      <c r="O257" t="b">
+      <c r="O257" t="n">
         <v>0</v>
       </c>
       <c r="P257" t="n">
@@ -61208,6 +61468,7 @@
       <c r="DX257" t="inlineStr"/>
       <c r="DY257" t="inlineStr"/>
       <c r="DZ257" t="inlineStr"/>
+      <c r="EA257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -61261,7 +61522,7 @@
       <c r="N258" t="n">
         <v>68</v>
       </c>
-      <c r="O258" t="b">
+      <c r="O258" t="n">
         <v>0</v>
       </c>
       <c r="P258" t="n">
@@ -61443,6 +61704,7 @@
       <c r="DX258" t="inlineStr"/>
       <c r="DY258" t="inlineStr"/>
       <c r="DZ258" t="inlineStr"/>
+      <c r="EA258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -61496,7 +61758,7 @@
       <c r="N259" t="n">
         <v>228</v>
       </c>
-      <c r="O259" t="b">
+      <c r="O259" t="n">
         <v>0</v>
       </c>
       <c r="P259" t="n">
@@ -61678,6 +61940,7 @@
       <c r="DX259" t="inlineStr"/>
       <c r="DY259" t="inlineStr"/>
       <c r="DZ259" t="inlineStr"/>
+      <c r="EA259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -61731,7 +61994,7 @@
       <c r="N260" t="n">
         <v>228</v>
       </c>
-      <c r="O260" t="b">
+      <c r="O260" t="n">
         <v>0</v>
       </c>
       <c r="P260" t="n">
@@ -61913,6 +62176,7 @@
       <c r="DX260" t="inlineStr"/>
       <c r="DY260" t="inlineStr"/>
       <c r="DZ260" t="inlineStr"/>
+      <c r="EA260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -61966,7 +62230,7 @@
       <c r="N261" t="n">
         <v>228</v>
       </c>
-      <c r="O261" t="b">
+      <c r="O261" t="n">
         <v>0</v>
       </c>
       <c r="P261" t="n">
@@ -62148,6 +62412,7 @@
       <c r="DX261" t="inlineStr"/>
       <c r="DY261" t="inlineStr"/>
       <c r="DZ261" t="inlineStr"/>
+      <c r="EA261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -62216,7 +62481,7 @@
       <c r="N262" t="n">
         <v>228</v>
       </c>
-      <c r="O262" t="b">
+      <c r="O262" t="n">
         <v>0</v>
       </c>
       <c r="P262" t="n">
@@ -62398,6 +62663,7 @@
       <c r="DX262" t="inlineStr"/>
       <c r="DY262" t="inlineStr"/>
       <c r="DZ262" t="inlineStr"/>
+      <c r="EA262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -62451,7 +62717,7 @@
       <c r="N263" t="n">
         <v>228</v>
       </c>
-      <c r="O263" t="b">
+      <c r="O263" t="n">
         <v>0</v>
       </c>
       <c r="P263" t="n">
@@ -62633,6 +62899,7 @@
       <c r="DX263" t="inlineStr"/>
       <c r="DY263" t="inlineStr"/>
       <c r="DZ263" t="inlineStr"/>
+      <c r="EA263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -62686,7 +62953,7 @@
       <c r="N264" t="n">
         <v>228</v>
       </c>
-      <c r="O264" t="b">
+      <c r="O264" t="n">
         <v>0</v>
       </c>
       <c r="P264" t="n">
@@ -62868,6 +63135,7 @@
       <c r="DX264" t="inlineStr"/>
       <c r="DY264" t="inlineStr"/>
       <c r="DZ264" t="inlineStr"/>
+      <c r="EA264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -62921,7 +63189,7 @@
       <c r="N265" t="n">
         <v>68</v>
       </c>
-      <c r="O265" t="b">
+      <c r="O265" t="n">
         <v>0</v>
       </c>
       <c r="P265" t="n">
@@ -63103,6 +63371,7 @@
       <c r="DX265" t="inlineStr"/>
       <c r="DY265" t="inlineStr"/>
       <c r="DZ265" t="inlineStr"/>
+      <c r="EA265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -63156,7 +63425,7 @@
       <c r="N266" t="n">
         <v>68</v>
       </c>
-      <c r="O266" t="b">
+      <c r="O266" t="n">
         <v>0</v>
       </c>
       <c r="P266" t="n">
@@ -63338,6 +63607,7 @@
       <c r="DX266" t="inlineStr"/>
       <c r="DY266" t="inlineStr"/>
       <c r="DZ266" t="inlineStr"/>
+      <c r="EA266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -63391,7 +63661,7 @@
       <c r="N267" t="n">
         <v>68</v>
       </c>
-      <c r="O267" t="b">
+      <c r="O267" t="n">
         <v>0</v>
       </c>
       <c r="P267" t="n">
@@ -63573,6 +63843,7 @@
       <c r="DX267" t="inlineStr"/>
       <c r="DY267" t="inlineStr"/>
       <c r="DZ267" t="inlineStr"/>
+      <c r="EA267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -63626,7 +63897,7 @@
       <c r="N268" t="n">
         <v>228</v>
       </c>
-      <c r="O268" t="b">
+      <c r="O268" t="n">
         <v>0</v>
       </c>
       <c r="P268" t="n">
@@ -63808,6 +64079,7 @@
       <c r="DX268" t="inlineStr"/>
       <c r="DY268" t="inlineStr"/>
       <c r="DZ268" t="inlineStr"/>
+      <c r="EA268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -63861,7 +64133,7 @@
       <c r="N269" t="n">
         <v>228</v>
       </c>
-      <c r="O269" t="b">
+      <c r="O269" t="n">
         <v>0</v>
       </c>
       <c r="P269" t="n">
@@ -64043,6 +64315,7 @@
       <c r="DX269" t="inlineStr"/>
       <c r="DY269" t="inlineStr"/>
       <c r="DZ269" t="inlineStr"/>
+      <c r="EA269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -64097,7 +64370,7 @@
       <c r="N270" t="n">
         <v>68</v>
       </c>
-      <c r="O270" t="b">
+      <c r="O270" t="n">
         <v>0</v>
       </c>
       <c r="P270" t="n">
@@ -64279,6 +64552,7 @@
       <c r="DX270" t="inlineStr"/>
       <c r="DY270" t="inlineStr"/>
       <c r="DZ270" t="inlineStr"/>
+      <c r="EA270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -64333,7 +64607,7 @@
       <c r="N271" t="n">
         <v>68</v>
       </c>
-      <c r="O271" t="b">
+      <c r="O271" t="n">
         <v>0</v>
       </c>
       <c r="P271" t="n">
@@ -64515,6 +64789,7 @@
       <c r="DX271" t="inlineStr"/>
       <c r="DY271" t="inlineStr"/>
       <c r="DZ271" t="inlineStr"/>
+      <c r="EA271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -64569,7 +64844,7 @@
       <c r="N272" t="n">
         <v>68</v>
       </c>
-      <c r="O272" t="b">
+      <c r="O272" t="n">
         <v>0</v>
       </c>
       <c r="P272" t="n">
@@ -64751,6 +65026,7 @@
       <c r="DX272" t="inlineStr"/>
       <c r="DY272" t="inlineStr"/>
       <c r="DZ272" t="inlineStr"/>
+      <c r="EA272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -64805,7 +65081,7 @@
       <c r="N273" t="n">
         <v>68</v>
       </c>
-      <c r="O273" t="b">
+      <c r="O273" t="n">
         <v>0</v>
       </c>
       <c r="P273" t="n">
@@ -64987,6 +65263,7 @@
       <c r="DX273" t="inlineStr"/>
       <c r="DY273" t="inlineStr"/>
       <c r="DZ273" t="inlineStr"/>
+      <c r="EA273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -65041,7 +65318,7 @@
       <c r="N274" t="n">
         <v>68</v>
       </c>
-      <c r="O274" t="b">
+      <c r="O274" t="n">
         <v>0</v>
       </c>
       <c r="P274" t="n">
@@ -65223,6 +65500,7 @@
       <c r="DX274" t="inlineStr"/>
       <c r="DY274" t="inlineStr"/>
       <c r="DZ274" t="inlineStr"/>
+      <c r="EA274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -65277,7 +65555,7 @@
       <c r="N275" t="n">
         <v>68</v>
       </c>
-      <c r="O275" t="b">
+      <c r="O275" t="n">
         <v>0</v>
       </c>
       <c r="P275" t="n">
@@ -65459,6 +65737,7 @@
       <c r="DX275" t="inlineStr"/>
       <c r="DY275" t="inlineStr"/>
       <c r="DZ275" t="inlineStr"/>
+      <c r="EA275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -65513,7 +65792,7 @@
       <c r="N276" t="n">
         <v>68</v>
       </c>
-      <c r="O276" t="b">
+      <c r="O276" t="n">
         <v>0</v>
       </c>
       <c r="P276" t="n">
@@ -65695,6 +65974,7 @@
       <c r="DX276" t="inlineStr"/>
       <c r="DY276" t="inlineStr"/>
       <c r="DZ276" t="inlineStr"/>
+      <c r="EA276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -65749,7 +66029,7 @@
       <c r="N277" t="n">
         <v>68</v>
       </c>
-      <c r="O277" t="b">
+      <c r="O277" t="n">
         <v>0</v>
       </c>
       <c r="P277" t="n">
@@ -65931,6 +66211,7 @@
       <c r="DX277" t="inlineStr"/>
       <c r="DY277" t="inlineStr"/>
       <c r="DZ277" t="inlineStr"/>
+      <c r="EA277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -65985,7 +66266,7 @@
       <c r="N278" t="n">
         <v>68</v>
       </c>
-      <c r="O278" t="b">
+      <c r="O278" t="n">
         <v>0</v>
       </c>
       <c r="P278" t="n">
@@ -66167,6 +66448,7 @@
       <c r="DX278" t="inlineStr"/>
       <c r="DY278" t="inlineStr"/>
       <c r="DZ278" t="inlineStr"/>
+      <c r="EA278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -66221,7 +66503,7 @@
       <c r="N279" t="n">
         <v>68</v>
       </c>
-      <c r="O279" t="b">
+      <c r="O279" t="n">
         <v>0</v>
       </c>
       <c r="P279" t="n">
@@ -66403,6 +66685,7 @@
       <c r="DX279" t="inlineStr"/>
       <c r="DY279" t="inlineStr"/>
       <c r="DZ279" t="inlineStr"/>
+      <c r="EA279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -66457,7 +66740,7 @@
       <c r="N280" t="n">
         <v>68</v>
       </c>
-      <c r="O280" t="b">
+      <c r="O280" t="n">
         <v>0</v>
       </c>
       <c r="P280" t="n">
@@ -66639,6 +66922,7 @@
       <c r="DX280" t="inlineStr"/>
       <c r="DY280" t="inlineStr"/>
       <c r="DZ280" t="inlineStr"/>
+      <c r="EA280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -66693,7 +66977,7 @@
       <c r="N281" t="n">
         <v>68</v>
       </c>
-      <c r="O281" t="b">
+      <c r="O281" t="n">
         <v>0</v>
       </c>
       <c r="P281" t="n">
@@ -66875,6 +67159,7 @@
       <c r="DX281" t="inlineStr"/>
       <c r="DY281" t="inlineStr"/>
       <c r="DZ281" t="inlineStr"/>
+      <c r="EA281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -66929,7 +67214,7 @@
       <c r="N282" t="n">
         <v>68</v>
       </c>
-      <c r="O282" t="b">
+      <c r="O282" t="n">
         <v>0</v>
       </c>
       <c r="P282" t="n">
@@ -67111,6 +67396,7 @@
       <c r="DX282" t="inlineStr"/>
       <c r="DY282" t="inlineStr"/>
       <c r="DZ282" t="inlineStr"/>
+      <c r="EA282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -67167,7 +67453,7 @@
       <c r="N283" t="n">
         <v>68</v>
       </c>
-      <c r="O283" t="b">
+      <c r="O283" t="n">
         <v>0</v>
       </c>
       <c r="P283" t="n">
@@ -67349,6 +67635,7 @@
       <c r="DX283" t="inlineStr"/>
       <c r="DY283" t="inlineStr"/>
       <c r="DZ283" t="inlineStr"/>
+      <c r="EA283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -67405,7 +67692,7 @@
       <c r="N284" t="n">
         <v>68</v>
       </c>
-      <c r="O284" t="b">
+      <c r="O284" t="n">
         <v>0</v>
       </c>
       <c r="P284" t="n">
@@ -67587,6 +67874,7 @@
       <c r="DX284" t="inlineStr"/>
       <c r="DY284" t="inlineStr"/>
       <c r="DZ284" t="inlineStr"/>
+      <c r="EA284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -67643,7 +67931,7 @@
       <c r="N285" t="n">
         <v>68</v>
       </c>
-      <c r="O285" t="b">
+      <c r="O285" t="n">
         <v>0</v>
       </c>
       <c r="P285" t="n">
@@ -67825,6 +68113,7 @@
       <c r="DX285" t="inlineStr"/>
       <c r="DY285" t="inlineStr"/>
       <c r="DZ285" t="inlineStr"/>
+      <c r="EA285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -67881,7 +68170,7 @@
       <c r="N286" t="n">
         <v>228</v>
       </c>
-      <c r="O286" t="b">
+      <c r="O286" t="n">
         <v>0</v>
       </c>
       <c r="P286" t="n">
@@ -68063,6 +68352,7 @@
       <c r="DX286" t="inlineStr"/>
       <c r="DY286" t="inlineStr"/>
       <c r="DZ286" t="inlineStr"/>
+      <c r="EA286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -68116,7 +68406,7 @@
       <c r="N287" t="n">
         <v>228</v>
       </c>
-      <c r="O287" t="b">
+      <c r="O287" t="n">
         <v>0</v>
       </c>
       <c r="P287" t="n">
@@ -68298,6 +68588,7 @@
       <c r="DX287" t="inlineStr"/>
       <c r="DY287" t="inlineStr"/>
       <c r="DZ287" t="inlineStr"/>
+      <c r="EA287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -68351,7 +68642,7 @@
       <c r="N288" t="n">
         <v>228</v>
       </c>
-      <c r="O288" t="b">
+      <c r="O288" t="n">
         <v>0</v>
       </c>
       <c r="P288" t="n">
@@ -68533,6 +68824,7 @@
       <c r="DX288" t="inlineStr"/>
       <c r="DY288" t="inlineStr"/>
       <c r="DZ288" t="inlineStr"/>
+      <c r="EA288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -68586,7 +68878,7 @@
       <c r="N289" t="n">
         <v>228</v>
       </c>
-      <c r="O289" t="b">
+      <c r="O289" t="n">
         <v>0</v>
       </c>
       <c r="P289" t="n">
@@ -68768,6 +69060,7 @@
       <c r="DX289" t="inlineStr"/>
       <c r="DY289" t="inlineStr"/>
       <c r="DZ289" t="inlineStr"/>
+      <c r="EA289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -68821,7 +69114,7 @@
       <c r="N290" t="n">
         <v>68</v>
       </c>
-      <c r="O290" t="b">
+      <c r="O290" t="n">
         <v>0</v>
       </c>
       <c r="P290" t="n">
@@ -69003,6 +69296,7 @@
       <c r="DX290" t="inlineStr"/>
       <c r="DY290" t="inlineStr"/>
       <c r="DZ290" t="inlineStr"/>
+      <c r="EA290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -69056,7 +69350,7 @@
       <c r="N291" t="n">
         <v>6</v>
       </c>
-      <c r="O291" t="b">
+      <c r="O291" t="n">
         <v>0</v>
       </c>
       <c r="P291" t="n">
@@ -69238,6 +69532,7 @@
       <c r="DX291" t="inlineStr"/>
       <c r="DY291" t="inlineStr"/>
       <c r="DZ291" t="inlineStr"/>
+      <c r="EA291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -69291,7 +69586,7 @@
       <c r="N292" t="n">
         <v>6</v>
       </c>
-      <c r="O292" t="b">
+      <c r="O292" t="n">
         <v>0</v>
       </c>
       <c r="P292" t="n">
@@ -69473,6 +69768,7 @@
       <c r="DX292" t="inlineStr"/>
       <c r="DY292" t="inlineStr"/>
       <c r="DZ292" t="inlineStr"/>
+      <c r="EA292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -69526,7 +69822,7 @@
       <c r="N293" t="n">
         <v>6</v>
       </c>
-      <c r="O293" t="b">
+      <c r="O293" t="n">
         <v>0</v>
       </c>
       <c r="P293" t="n">
@@ -69708,6 +70004,7 @@
       <c r="DX293" t="inlineStr"/>
       <c r="DY293" t="inlineStr"/>
       <c r="DZ293" t="inlineStr"/>
+      <c r="EA293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -69761,7 +70058,7 @@
       <c r="N294" t="n">
         <v>6</v>
       </c>
-      <c r="O294" t="b">
+      <c r="O294" t="n">
         <v>0</v>
       </c>
       <c r="P294" t="n">
@@ -69943,6 +70240,7 @@
       <c r="DX294" t="inlineStr"/>
       <c r="DY294" t="inlineStr"/>
       <c r="DZ294" t="inlineStr"/>
+      <c r="EA294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -69996,7 +70294,7 @@
       <c r="N295" t="n">
         <v>6</v>
       </c>
-      <c r="O295" t="b">
+      <c r="O295" t="n">
         <v>0</v>
       </c>
       <c r="P295" t="n">
@@ -70178,6 +70476,7 @@
       <c r="DX295" t="inlineStr"/>
       <c r="DY295" t="inlineStr"/>
       <c r="DZ295" t="inlineStr"/>
+      <c r="EA295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -70231,7 +70530,7 @@
       <c r="N296" t="n">
         <v>6</v>
       </c>
-      <c r="O296" t="b">
+      <c r="O296" t="n">
         <v>0</v>
       </c>
       <c r="P296" t="n">
@@ -70413,6 +70712,7 @@
       <c r="DX296" t="inlineStr"/>
       <c r="DY296" t="inlineStr"/>
       <c r="DZ296" t="inlineStr"/>
+      <c r="EA296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -70466,7 +70766,7 @@
       <c r="N297" t="n">
         <v>6</v>
       </c>
-      <c r="O297" t="b">
+      <c r="O297" t="n">
         <v>0</v>
       </c>
       <c r="P297" t="n">
@@ -70648,6 +70948,7 @@
       <c r="DX297" t="inlineStr"/>
       <c r="DY297" t="inlineStr"/>
       <c r="DZ297" t="inlineStr"/>
+      <c r="EA297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -70701,7 +71002,7 @@
       <c r="N298" t="n">
         <v>6</v>
       </c>
-      <c r="O298" t="b">
+      <c r="O298" t="n">
         <v>0</v>
       </c>
       <c r="P298" t="n">
@@ -70883,6 +71184,7 @@
       <c r="DX298" t="inlineStr"/>
       <c r="DY298" t="inlineStr"/>
       <c r="DZ298" t="inlineStr"/>
+      <c r="EA298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -70936,7 +71238,7 @@
       <c r="N299" t="n">
         <v>6</v>
       </c>
-      <c r="O299" t="b">
+      <c r="O299" t="n">
         <v>0</v>
       </c>
       <c r="P299" t="n">
@@ -71118,6 +71420,7 @@
       <c r="DX299" t="inlineStr"/>
       <c r="DY299" t="inlineStr"/>
       <c r="DZ299" t="inlineStr"/>
+      <c r="EA299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -71171,7 +71474,7 @@
       <c r="N300" t="n">
         <v>6</v>
       </c>
-      <c r="O300" t="b">
+      <c r="O300" t="n">
         <v>0</v>
       </c>
       <c r="P300" t="n">
@@ -71353,6 +71656,7 @@
       <c r="DX300" t="inlineStr"/>
       <c r="DY300" t="inlineStr"/>
       <c r="DZ300" t="inlineStr"/>
+      <c r="EA300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -71406,7 +71710,7 @@
       <c r="N301" t="n">
         <v>6</v>
       </c>
-      <c r="O301" t="b">
+      <c r="O301" t="n">
         <v>0</v>
       </c>
       <c r="P301" t="n">
@@ -71588,6 +71892,7 @@
       <c r="DX301" t="inlineStr"/>
       <c r="DY301" t="inlineStr"/>
       <c r="DZ301" t="inlineStr"/>
+      <c r="EA301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -71641,7 +71946,7 @@
       <c r="N302" t="n">
         <v>6</v>
       </c>
-      <c r="O302" t="b">
+      <c r="O302" t="n">
         <v>0</v>
       </c>
       <c r="P302" t="n">
@@ -71823,6 +72128,7 @@
       <c r="DX302" t="inlineStr"/>
       <c r="DY302" t="inlineStr"/>
       <c r="DZ302" t="inlineStr"/>
+      <c r="EA302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -71876,7 +72182,7 @@
       <c r="N303" t="n">
         <v>6</v>
       </c>
-      <c r="O303" t="b">
+      <c r="O303" t="n">
         <v>0</v>
       </c>
       <c r="P303" t="n">
@@ -72058,6 +72364,7 @@
       <c r="DX303" t="inlineStr"/>
       <c r="DY303" t="inlineStr"/>
       <c r="DZ303" t="inlineStr"/>
+      <c r="EA303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -72111,7 +72418,7 @@
       <c r="N304" t="n">
         <v>6</v>
       </c>
-      <c r="O304" t="b">
+      <c r="O304" t="n">
         <v>0</v>
       </c>
       <c r="P304" t="n">
@@ -72293,6 +72600,7 @@
       <c r="DX304" t="inlineStr"/>
       <c r="DY304" t="inlineStr"/>
       <c r="DZ304" t="inlineStr"/>
+      <c r="EA304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -72346,7 +72654,7 @@
       <c r="N305" t="n">
         <v>6</v>
       </c>
-      <c r="O305" t="b">
+      <c r="O305" t="n">
         <v>0</v>
       </c>
       <c r="P305" t="n">
@@ -72528,6 +72836,7 @@
       <c r="DX305" t="inlineStr"/>
       <c r="DY305" t="inlineStr"/>
       <c r="DZ305" t="inlineStr"/>
+      <c r="EA305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -72581,7 +72890,7 @@
       <c r="N306" t="n">
         <v>6</v>
       </c>
-      <c r="O306" t="b">
+      <c r="O306" t="n">
         <v>0</v>
       </c>
       <c r="P306" t="n">
@@ -72763,6 +73072,7 @@
       <c r="DX306" t="inlineStr"/>
       <c r="DY306" t="inlineStr"/>
       <c r="DZ306" t="inlineStr"/>
+      <c r="EA306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -72816,7 +73126,7 @@
       <c r="N307" t="n">
         <v>6</v>
       </c>
-      <c r="O307" t="b">
+      <c r="O307" t="n">
         <v>0</v>
       </c>
       <c r="P307" t="n">
@@ -72998,6 +73308,7 @@
       <c r="DX307" t="inlineStr"/>
       <c r="DY307" t="inlineStr"/>
       <c r="DZ307" t="inlineStr"/>
+      <c r="EA307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -73051,7 +73362,7 @@
       <c r="N308" t="n">
         <v>6</v>
       </c>
-      <c r="O308" t="b">
+      <c r="O308" t="n">
         <v>0</v>
       </c>
       <c r="P308" t="n">
@@ -73393,6 +73704,7 @@
       <c r="DX308" t="inlineStr"/>
       <c r="DY308" t="inlineStr"/>
       <c r="DZ308" t="inlineStr"/>
+      <c r="EA308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -73446,7 +73758,7 @@
       <c r="N309" t="n">
         <v>6</v>
       </c>
-      <c r="O309" t="b">
+      <c r="O309" t="n">
         <v>0</v>
       </c>
       <c r="P309" t="n">
@@ -73688,6 +74000,7 @@
       <c r="DX309" t="inlineStr"/>
       <c r="DY309" t="inlineStr"/>
       <c r="DZ309" t="inlineStr"/>
+      <c r="EA309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -73741,7 +74054,7 @@
       <c r="N310" t="n">
         <v>6</v>
       </c>
-      <c r="O310" t="b">
+      <c r="O310" t="n">
         <v>0</v>
       </c>
       <c r="P310" t="n">
@@ -73983,6 +74296,7 @@
       <c r="DX310" t="inlineStr"/>
       <c r="DY310" t="inlineStr"/>
       <c r="DZ310" t="inlineStr"/>
+      <c r="EA310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -74036,7 +74350,7 @@
       <c r="N311" t="n">
         <v>6</v>
       </c>
-      <c r="O311" t="b">
+      <c r="O311" t="n">
         <v>0</v>
       </c>
       <c r="P311" t="n">
@@ -74278,6 +74592,7 @@
       <c r="DX311" t="inlineStr"/>
       <c r="DY311" t="inlineStr"/>
       <c r="DZ311" t="inlineStr"/>
+      <c r="EA311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -74331,7 +74646,7 @@
       <c r="N312" t="n">
         <v>6</v>
       </c>
-      <c r="O312" t="b">
+      <c r="O312" t="n">
         <v>0</v>
       </c>
       <c r="P312" t="n">
@@ -74573,6 +74888,7 @@
       <c r="DX312" t="inlineStr"/>
       <c r="DY312" t="inlineStr"/>
       <c r="DZ312" t="inlineStr"/>
+      <c r="EA312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -74626,7 +74942,7 @@
       <c r="N313" t="n">
         <v>6</v>
       </c>
-      <c r="O313" t="b">
+      <c r="O313" t="n">
         <v>0</v>
       </c>
       <c r="P313" t="n">
@@ -74868,6 +75184,7 @@
       <c r="DX313" t="inlineStr"/>
       <c r="DY313" t="inlineStr"/>
       <c r="DZ313" t="inlineStr"/>
+      <c r="EA313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -74921,7 +75238,7 @@
       <c r="N314" t="n">
         <v>6</v>
       </c>
-      <c r="O314" t="b">
+      <c r="O314" t="n">
         <v>0</v>
       </c>
       <c r="P314" t="n">
@@ -75163,6 +75480,7 @@
       <c r="DX314" t="inlineStr"/>
       <c r="DY314" t="inlineStr"/>
       <c r="DZ314" t="inlineStr"/>
+      <c r="EA314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -75216,7 +75534,7 @@
       <c r="N315" t="n">
         <v>6</v>
       </c>
-      <c r="O315" t="b">
+      <c r="O315" t="n">
         <v>0</v>
       </c>
       <c r="P315" t="n">
@@ -75458,6 +75776,7 @@
       <c r="DX315" t="inlineStr"/>
       <c r="DY315" t="inlineStr"/>
       <c r="DZ315" t="inlineStr"/>
+      <c r="EA315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -75511,7 +75830,7 @@
       <c r="N316" t="n">
         <v>228</v>
       </c>
-      <c r="O316" t="b">
+      <c r="O316" t="n">
         <v>0</v>
       </c>
       <c r="P316" t="n">
@@ -75753,6 +76072,7 @@
       <c r="DX316" t="inlineStr"/>
       <c r="DY316" t="inlineStr"/>
       <c r="DZ316" t="inlineStr"/>
+      <c r="EA316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -75806,7 +76126,7 @@
       <c r="N317" t="n">
         <v>228</v>
       </c>
-      <c r="O317" t="b">
+      <c r="O317" t="n">
         <v>0</v>
       </c>
       <c r="P317" t="n">
@@ -76048,6 +76368,7 @@
       <c r="DX317" t="inlineStr"/>
       <c r="DY317" t="inlineStr"/>
       <c r="DZ317" t="inlineStr"/>
+      <c r="EA317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -76101,7 +76422,7 @@
       <c r="N318" t="n">
         <v>228</v>
       </c>
-      <c r="O318" t="b">
+      <c r="O318" t="n">
         <v>0</v>
       </c>
       <c r="P318" t="n">
@@ -76343,6 +76664,7 @@
       <c r="DX318" t="inlineStr"/>
       <c r="DY318" t="inlineStr"/>
       <c r="DZ318" t="inlineStr"/>
+      <c r="EA318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -76396,7 +76718,7 @@
       <c r="N319" t="n">
         <v>68</v>
       </c>
-      <c r="O319" t="b">
+      <c r="O319" t="n">
         <v>0</v>
       </c>
       <c r="P319" t="n">
@@ -76638,6 +76960,7 @@
       <c r="DX319" t="inlineStr"/>
       <c r="DY319" t="inlineStr"/>
       <c r="DZ319" t="inlineStr"/>
+      <c r="EA319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -76691,7 +77014,7 @@
       <c r="N320" t="n">
         <v>28</v>
       </c>
-      <c r="O320" t="b">
+      <c r="O320" t="n">
         <v>0</v>
       </c>
       <c r="P320" t="n">
@@ -76933,6 +77256,7 @@
       <c r="DX320" t="inlineStr"/>
       <c r="DY320" t="inlineStr"/>
       <c r="DZ320" t="inlineStr"/>
+      <c r="EA320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -76986,7 +77310,7 @@
       <c r="N321" t="n">
         <v>28</v>
       </c>
-      <c r="O321" t="b">
+      <c r="O321" t="n">
         <v>0</v>
       </c>
       <c r="P321" t="n">
@@ -77228,6 +77552,7 @@
       <c r="DX321" t="inlineStr"/>
       <c r="DY321" t="inlineStr"/>
       <c r="DZ321" t="inlineStr"/>
+      <c r="EA321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -77281,7 +77606,7 @@
       <c r="N322" t="n">
         <v>228</v>
       </c>
-      <c r="O322" t="b">
+      <c r="O322" t="n">
         <v>0</v>
       </c>
       <c r="P322" t="n">
@@ -77523,6 +77848,7 @@
       <c r="DX322" t="inlineStr"/>
       <c r="DY322" t="inlineStr"/>
       <c r="DZ322" t="inlineStr"/>
+      <c r="EA322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -77576,7 +77902,7 @@
       <c r="N323" t="n">
         <v>228</v>
       </c>
-      <c r="O323" t="b">
+      <c r="O323" t="n">
         <v>0</v>
       </c>
       <c r="P323" t="n">
@@ -77818,6 +78144,7 @@
       <c r="DX323" t="inlineStr"/>
       <c r="DY323" t="inlineStr"/>
       <c r="DZ323" t="inlineStr"/>
+      <c r="EA323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -77871,7 +78198,7 @@
       <c r="N324" t="n">
         <v>228</v>
       </c>
-      <c r="O324" t="b">
+      <c r="O324" t="n">
         <v>0</v>
       </c>
       <c r="P324" t="n">
@@ -78113,6 +78440,7 @@
       <c r="DX324" t="inlineStr"/>
       <c r="DY324" t="inlineStr"/>
       <c r="DZ324" t="inlineStr"/>
+      <c r="EA324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -78166,7 +78494,7 @@
       <c r="N325" t="n">
         <v>228</v>
       </c>
-      <c r="O325" t="b">
+      <c r="O325" t="n">
         <v>1</v>
       </c>
       <c r="P325" t="n">
@@ -78221,7 +78549,7 @@
         <v>0</v>
       </c>
       <c r="AG325" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH325" t="n">
         <v>0</v>
@@ -78248,7 +78576,7 @@
         <v>0</v>
       </c>
       <c r="AP325" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ325" t="n">
         <v>0</v>
@@ -78272,7 +78600,7 @@
         <v>0</v>
       </c>
       <c r="AX325" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AY325" t="n">
         <v>0</v>
@@ -78284,7 +78612,7 @@
         <v>0</v>
       </c>
       <c r="BB325" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC325" t="n">
         <v>0</v>
@@ -78299,7 +78627,7 @@
         <v>1.25328357850631e-06</v>
       </c>
       <c r="BG325" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BH325" t="n">
         <v>0</v>
@@ -78344,16 +78672,16 @@
         <v>0</v>
       </c>
       <c r="BV325" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW325" t="n">
         <v>0</v>
       </c>
       <c r="BX325" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY325" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BZ325" t="inlineStr"/>
       <c r="CA325" t="inlineStr"/>
@@ -78414,6 +78742,1196 @@
       <c r="DZ325" t="n">
         <v>1.39421021493597</v>
       </c>
+      <c r="EA325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Pairwise Ranking</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>10</v>
+      </c>
+      <c r="C326" t="n">
+        <v>100</v>
+      </c>
+      <c r="D326" t="n">
+        <v>5</v>
+      </c>
+      <c r="E326" t="n">
+        <v>50</v>
+      </c>
+      <c r="F326" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G326" t="n">
+        <v>50</v>
+      </c>
+      <c r="H326" t="n">
+        <v>5</v>
+      </c>
+      <c r="I326" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>bic</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>[0.00354813 0.00458259 0.00591864 0.00764422 0.00987289 0.01275133
+ 0.01646898 0.0212705  0.02747191 0.03548134]</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="N326" t="n">
+        <v>228</v>
+      </c>
+      <c r="O326" t="inlineStr"/>
+      <c r="P326" t="n">
+        <v>1.240044317683098</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>0.05553195038611911</v>
+      </c>
+      <c r="R326" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="S326" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="T326" t="n">
+        <v>1</v>
+      </c>
+      <c r="U326" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="V326" t="n">
+        <v>0.9996461961974425</v>
+      </c>
+      <c r="W326" t="n">
+        <v>0.9828868868868869</v>
+      </c>
+      <c r="X326" t="n">
+        <v>1.418463366617676</v>
+      </c>
+      <c r="Y326" t="n">
+        <v>0.4799929031052887</v>
+      </c>
+      <c r="Z326" t="n">
+        <v>0.4654057322642898</v>
+      </c>
+      <c r="AA326" t="n">
+        <v>0.4040135672043904</v>
+      </c>
+      <c r="AB326" t="n">
+        <v>0.4631273378712608</v>
+      </c>
+      <c r="AC326" t="n">
+        <v>0.4186055046457008</v>
+      </c>
+      <c r="AD326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL326" t="n">
+        <v>0.007736617018222726</v>
+      </c>
+      <c r="AM326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS326" t="n">
+        <v>398887</v>
+      </c>
+      <c r="AT326" t="n">
+        <v>347822</v>
+      </c>
+      <c r="AU326" t="n">
+        <v>0.8719812879336755</v>
+      </c>
+      <c r="AV326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ326" t="n">
+        <v>2.307728312132777e-06</v>
+      </c>
+      <c r="BA326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF326" t="n">
+        <v>1.25328357850631e-06</v>
+      </c>
+      <c r="BG326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK326" t="n">
+        <v>2.386366772555685e-06</v>
+      </c>
+      <c r="BL326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ326" t="inlineStr"/>
+      <c r="CA326" t="inlineStr"/>
+      <c r="CB326" t="inlineStr"/>
+      <c r="CC326" t="inlineStr"/>
+      <c r="CD326" t="inlineStr"/>
+      <c r="CE326" t="inlineStr"/>
+      <c r="CF326" t="inlineStr"/>
+      <c r="CG326" t="inlineStr"/>
+      <c r="CH326" t="inlineStr"/>
+      <c r="CI326" t="inlineStr"/>
+      <c r="CJ326" t="inlineStr"/>
+      <c r="CK326" t="inlineStr"/>
+      <c r="CL326" t="inlineStr"/>
+      <c r="CM326" t="inlineStr"/>
+      <c r="CN326" t="inlineStr"/>
+      <c r="CO326" t="inlineStr"/>
+      <c r="CP326" t="inlineStr"/>
+      <c r="CQ326" t="inlineStr"/>
+      <c r="CR326" t="inlineStr"/>
+      <c r="CS326" t="inlineStr"/>
+      <c r="CT326" t="inlineStr"/>
+      <c r="CU326" t="inlineStr"/>
+      <c r="CV326" t="inlineStr"/>
+      <c r="CW326" t="inlineStr"/>
+      <c r="CX326" t="inlineStr"/>
+      <c r="CY326" t="inlineStr"/>
+      <c r="CZ326" t="inlineStr"/>
+      <c r="DA326" t="inlineStr"/>
+      <c r="DB326" t="inlineStr"/>
+      <c r="DC326" t="inlineStr"/>
+      <c r="DD326" t="inlineStr"/>
+      <c r="DE326" t="inlineStr"/>
+      <c r="DF326" t="inlineStr"/>
+      <c r="DG326" t="inlineStr"/>
+      <c r="DH326" t="inlineStr"/>
+      <c r="DI326" t="inlineStr"/>
+      <c r="DJ326" t="inlineStr"/>
+      <c r="DK326" t="inlineStr"/>
+      <c r="DL326" t="inlineStr"/>
+      <c r="DM326" t="inlineStr"/>
+      <c r="DN326" t="inlineStr"/>
+      <c r="DO326" t="inlineStr"/>
+      <c r="DP326" t="inlineStr"/>
+      <c r="DQ326" t="inlineStr"/>
+      <c r="DR326" t="inlineStr"/>
+      <c r="DS326" t="inlineStr"/>
+      <c r="DT326" t="inlineStr"/>
+      <c r="DU326" t="inlineStr"/>
+      <c r="DV326" t="inlineStr"/>
+      <c r="DW326" t="inlineStr"/>
+      <c r="DX326" t="n">
+        <v>1.334588351796431</v>
+      </c>
+      <c r="DY326" t="n">
+        <v>1.80264360104337</v>
+      </c>
+      <c r="DZ326" t="n">
+        <v>1.39421021493597</v>
+      </c>
+      <c r="EA326" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Pairwise Ranking</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>10</v>
+      </c>
+      <c r="C327" t="n">
+        <v>100</v>
+      </c>
+      <c r="D327" t="n">
+        <v>5</v>
+      </c>
+      <c r="E327" t="n">
+        <v>50</v>
+      </c>
+      <c r="F327" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G327" t="n">
+        <v>50</v>
+      </c>
+      <c r="H327" t="n">
+        <v>5</v>
+      </c>
+      <c r="I327" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>bic</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr"/>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="N327" t="n">
+        <v>228</v>
+      </c>
+      <c r="O327" t="inlineStr"/>
+      <c r="P327" t="n">
+        <v>1.240044317683098</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>0.05553195038611911</v>
+      </c>
+      <c r="R327" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="S327" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="T327" t="n">
+        <v>1</v>
+      </c>
+      <c r="U327" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="V327" t="n">
+        <v>0.9996461961974425</v>
+      </c>
+      <c r="W327" t="n">
+        <v>0.9828868868868869</v>
+      </c>
+      <c r="X327" t="n">
+        <v>1.418463366617676</v>
+      </c>
+      <c r="Y327" t="n">
+        <v>0.4799929031052887</v>
+      </c>
+      <c r="Z327" t="n">
+        <v>0.4654057322642898</v>
+      </c>
+      <c r="AA327" t="n">
+        <v>0.4040135672043904</v>
+      </c>
+      <c r="AB327" t="n">
+        <v>0.4631273378712608</v>
+      </c>
+      <c r="AC327" t="n">
+        <v>0.4186055046457008</v>
+      </c>
+      <c r="AD327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL327" t="n">
+        <v>0.007736617018222726</v>
+      </c>
+      <c r="AM327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS327" t="n">
+        <v>398887</v>
+      </c>
+      <c r="AT327" t="n">
+        <v>347822</v>
+      </c>
+      <c r="AU327" t="n">
+        <v>0.8719812879336755</v>
+      </c>
+      <c r="AV327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ327" t="n">
+        <v>2.307728312132777e-06</v>
+      </c>
+      <c r="BA327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF327" t="n">
+        <v>1.25328357850631e-06</v>
+      </c>
+      <c r="BG327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK327" t="n">
+        <v>2.386366772555685e-06</v>
+      </c>
+      <c r="BL327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ327" t="inlineStr"/>
+      <c r="CA327" t="inlineStr"/>
+      <c r="CB327" t="inlineStr"/>
+      <c r="CC327" t="inlineStr"/>
+      <c r="CD327" t="inlineStr"/>
+      <c r="CE327" t="inlineStr"/>
+      <c r="CF327" t="inlineStr"/>
+      <c r="CG327" t="inlineStr"/>
+      <c r="CH327" t="inlineStr"/>
+      <c r="CI327" t="inlineStr"/>
+      <c r="CJ327" t="inlineStr"/>
+      <c r="CK327" t="inlineStr"/>
+      <c r="CL327" t="inlineStr"/>
+      <c r="CM327" t="inlineStr"/>
+      <c r="CN327" t="inlineStr"/>
+      <c r="CO327" t="inlineStr"/>
+      <c r="CP327" t="inlineStr"/>
+      <c r="CQ327" t="inlineStr"/>
+      <c r="CR327" t="inlineStr"/>
+      <c r="CS327" t="inlineStr"/>
+      <c r="CT327" t="inlineStr"/>
+      <c r="CU327" t="inlineStr"/>
+      <c r="CV327" t="inlineStr"/>
+      <c r="CW327" t="inlineStr"/>
+      <c r="CX327" t="inlineStr"/>
+      <c r="CY327" t="inlineStr"/>
+      <c r="CZ327" t="inlineStr"/>
+      <c r="DA327" t="inlineStr"/>
+      <c r="DB327" t="inlineStr"/>
+      <c r="DC327" t="inlineStr"/>
+      <c r="DD327" t="inlineStr"/>
+      <c r="DE327" t="inlineStr"/>
+      <c r="DF327" t="inlineStr"/>
+      <c r="DG327" t="inlineStr"/>
+      <c r="DH327" t="inlineStr"/>
+      <c r="DI327" t="inlineStr"/>
+      <c r="DJ327" t="inlineStr"/>
+      <c r="DK327" t="inlineStr"/>
+      <c r="DL327" t="inlineStr"/>
+      <c r="DM327" t="inlineStr"/>
+      <c r="DN327" t="inlineStr"/>
+      <c r="DO327" t="inlineStr"/>
+      <c r="DP327" t="inlineStr"/>
+      <c r="DQ327" t="inlineStr"/>
+      <c r="DR327" t="inlineStr"/>
+      <c r="DS327" t="inlineStr"/>
+      <c r="DT327" t="inlineStr"/>
+      <c r="DU327" t="inlineStr"/>
+      <c r="DV327" t="inlineStr"/>
+      <c r="DW327" t="inlineStr"/>
+      <c r="DX327" t="n">
+        <v>1.334588351796431</v>
+      </c>
+      <c r="DY327" t="n">
+        <v>1.652967817235276</v>
+      </c>
+      <c r="DZ327" t="n">
+        <v>1.39421021493597</v>
+      </c>
+      <c r="EA327" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Pairwise Ranking</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>10</v>
+      </c>
+      <c r="C328" t="n">
+        <v>100</v>
+      </c>
+      <c r="D328" t="n">
+        <v>5</v>
+      </c>
+      <c r="E328" t="n">
+        <v>50</v>
+      </c>
+      <c r="F328" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G328" t="n">
+        <v>50</v>
+      </c>
+      <c r="H328" t="n">
+        <v>5</v>
+      </c>
+      <c r="I328" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>bic</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr"/>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N328" t="n">
+        <v>228</v>
+      </c>
+      <c r="O328" t="n">
+        <v>1</v>
+      </c>
+      <c r="P328" t="n">
+        <v>1.268681034810117</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>0.07010132639079805</v>
+      </c>
+      <c r="R328" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="S328" t="n">
+        <v>0.1470588235294118</v>
+      </c>
+      <c r="T328" t="n">
+        <v>1</v>
+      </c>
+      <c r="U328" t="n">
+        <v>0.2564102564102564</v>
+      </c>
+      <c r="V328" t="n">
+        <v>0.9939781729192707</v>
+      </c>
+      <c r="W328" t="n">
+        <v>0.929941941941942</v>
+      </c>
+      <c r="X328" t="n">
+        <v>1.441970692336081</v>
+      </c>
+      <c r="Y328" t="n">
+        <v>0.474584034755321</v>
+      </c>
+      <c r="Z328" t="n">
+        <v>0.4459863436854805</v>
+      </c>
+      <c r="AA328" t="n">
+        <v>0.4364623428594516</v>
+      </c>
+      <c r="AB328" t="n">
+        <v>0.381292998187258</v>
+      </c>
+      <c r="AC328" t="n">
+        <v>0.4568984964690546</v>
+      </c>
+      <c r="AD328" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE328" t="n">
+        <v>0.002753969971870236</v>
+      </c>
+      <c r="AF328" t="n">
+        <v>0.01002660491913113</v>
+      </c>
+      <c r="AG328" t="n">
+        <v>0.01120735480381563</v>
+      </c>
+      <c r="AH328" t="n">
+        <v>0.009605672107286942</v>
+      </c>
+      <c r="AI328" t="n">
+        <v>9.07540871144244e-06</v>
+      </c>
+      <c r="AJ328" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK328" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL328" t="n">
+        <v>0.0374064336975994</v>
+      </c>
+      <c r="AM328" t="n">
+        <v>0.02221554722892959</v>
+      </c>
+      <c r="AN328" t="n">
+        <v>0.02816482606028015</v>
+      </c>
+      <c r="AO328" t="n">
+        <v>5.361958818676391e-06</v>
+      </c>
+      <c r="AP328" t="n">
+        <v>0.0005424297078956535</v>
+      </c>
+      <c r="AQ328" t="n">
+        <v>0.01603571535893062</v>
+      </c>
+      <c r="AR328" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS328" t="n">
+        <v>399281</v>
+      </c>
+      <c r="AT328" t="n">
+        <v>385365</v>
+      </c>
+      <c r="AU328" t="n">
+        <v>0.9651473523658777</v>
+      </c>
+      <c r="AV328" t="n">
+        <v>0.04608859283436749</v>
+      </c>
+      <c r="AW328" t="n">
+        <v>1.015896711128352e-05</v>
+      </c>
+      <c r="AX328" t="n">
+        <v>0.0008171194706841345</v>
+      </c>
+      <c r="AY328" t="n">
+        <v>3.312576304569698e-06</v>
+      </c>
+      <c r="AZ328" t="n">
+        <v>0.06550918335663293</v>
+      </c>
+      <c r="BA328" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB328" t="n">
+        <v>2.698984903176955e-05</v>
+      </c>
+      <c r="BC328" t="n">
+        <v>0.006991166036418782</v>
+      </c>
+      <c r="BD328" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE328" t="n">
+        <v>0.01115641522032001</v>
+      </c>
+      <c r="BF328" t="n">
+        <v>0.001444615895823601</v>
+      </c>
+      <c r="BG328" t="n">
+        <v>0.01769532536541322</v>
+      </c>
+      <c r="BH328" t="n">
+        <v>0.02733727604846341</v>
+      </c>
+      <c r="BI328" t="n">
+        <v>0.04386019909945687</v>
+      </c>
+      <c r="BJ328" t="n">
+        <v>0.009237622055262348</v>
+      </c>
+      <c r="BK328" t="n">
+        <v>0.05747497062033919</v>
+      </c>
+      <c r="BL328" t="n">
+        <v>0.03848581082858284</v>
+      </c>
+      <c r="BM328" t="n">
+        <v>0.01744985064168763</v>
+      </c>
+      <c r="BN328" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO328" t="n">
+        <v>0.00777830710153274</v>
+      </c>
+      <c r="BP328" t="n">
+        <v>0.0915087282102495</v>
+      </c>
+      <c r="BQ328" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR328" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS328" t="n">
+        <v>0.02221834320247836</v>
+      </c>
+      <c r="BT328" t="n">
+        <v>6.416857638253277e-06</v>
+      </c>
+      <c r="BU328" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV328" t="n">
+        <v>0.005084696727527919</v>
+      </c>
+      <c r="BW328" t="n">
+        <v>0.06141245840236841</v>
+      </c>
+      <c r="BX328" t="n">
+        <v>0.01751731684088733</v>
+      </c>
+      <c r="BY328" t="n">
+        <v>0.01320266806461587</v>
+      </c>
+      <c r="BZ328" t="inlineStr"/>
+      <c r="CA328" t="inlineStr"/>
+      <c r="CB328" t="inlineStr"/>
+      <c r="CC328" t="inlineStr"/>
+      <c r="CD328" t="inlineStr"/>
+      <c r="CE328" t="inlineStr"/>
+      <c r="CF328" t="inlineStr"/>
+      <c r="CG328" t="inlineStr"/>
+      <c r="CH328" t="inlineStr"/>
+      <c r="CI328" t="inlineStr"/>
+      <c r="CJ328" t="inlineStr"/>
+      <c r="CK328" t="inlineStr"/>
+      <c r="CL328" t="inlineStr"/>
+      <c r="CM328" t="inlineStr"/>
+      <c r="CN328" t="inlineStr"/>
+      <c r="CO328" t="inlineStr"/>
+      <c r="CP328" t="inlineStr"/>
+      <c r="CQ328" t="inlineStr"/>
+      <c r="CR328" t="inlineStr"/>
+      <c r="CS328" t="inlineStr"/>
+      <c r="CT328" t="inlineStr"/>
+      <c r="CU328" t="inlineStr"/>
+      <c r="CV328" t="inlineStr"/>
+      <c r="CW328" t="inlineStr"/>
+      <c r="CX328" t="inlineStr"/>
+      <c r="CY328" t="inlineStr"/>
+      <c r="CZ328" t="inlineStr"/>
+      <c r="DA328" t="inlineStr"/>
+      <c r="DB328" t="inlineStr"/>
+      <c r="DC328" t="inlineStr"/>
+      <c r="DD328" t="inlineStr"/>
+      <c r="DE328" t="inlineStr"/>
+      <c r="DF328" t="inlineStr"/>
+      <c r="DG328" t="inlineStr"/>
+      <c r="DH328" t="inlineStr"/>
+      <c r="DI328" t="inlineStr"/>
+      <c r="DJ328" t="inlineStr"/>
+      <c r="DK328" t="inlineStr"/>
+      <c r="DL328" t="inlineStr"/>
+      <c r="DM328" t="inlineStr"/>
+      <c r="DN328" t="inlineStr"/>
+      <c r="DO328" t="inlineStr"/>
+      <c r="DP328" t="inlineStr"/>
+      <c r="DQ328" t="inlineStr"/>
+      <c r="DR328" t="inlineStr"/>
+      <c r="DS328" t="inlineStr"/>
+      <c r="DT328" t="inlineStr"/>
+      <c r="DU328" t="inlineStr"/>
+      <c r="DV328" t="inlineStr"/>
+      <c r="DW328" t="inlineStr"/>
+      <c r="DX328" t="n">
+        <v>1.34127372249319</v>
+      </c>
+      <c r="DY328" t="n">
+        <v>1.535624593731482</v>
+      </c>
+      <c r="DZ328" t="n">
+        <v>1.367703539970731</v>
+      </c>
+      <c r="EA328" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Pairwise Ranking</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>10</v>
+      </c>
+      <c r="C329" t="n">
+        <v>10</v>
+      </c>
+      <c r="D329" t="n">
+        <v>5</v>
+      </c>
+      <c r="E329" t="n">
+        <v>50</v>
+      </c>
+      <c r="F329" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G329" t="n">
+        <v>50</v>
+      </c>
+      <c r="H329" t="n">
+        <v>5</v>
+      </c>
+      <c r="I329" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>bic</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr"/>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N329" t="n">
+        <v>68</v>
+      </c>
+      <c r="O329" t="n">
+        <v>1</v>
+      </c>
+      <c r="P329" t="n">
+        <v>1.44826183022429</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>0.07756462693014024</v>
+      </c>
+      <c r="R329" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="S329" t="n">
+        <v>0.2631578947368421</v>
+      </c>
+      <c r="T329" t="n">
+        <v>1</v>
+      </c>
+      <c r="U329" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="V329" t="n">
+        <v>0.9842331978866294</v>
+      </c>
+      <c r="W329" t="n">
+        <v>0.8876767676767678</v>
+      </c>
+      <c r="X329" t="n">
+        <v>1.960536450628946</v>
+      </c>
+      <c r="Y329" t="n">
+        <v>0.2817057094633624</v>
+      </c>
+      <c r="Z329" t="n">
+        <v>0.6848750603967513</v>
+      </c>
+      <c r="AA329" t="n">
+        <v>0.3411583764687044</v>
+      </c>
+      <c r="AB329" t="n">
+        <v>0.3630691469015841</v>
+      </c>
+      <c r="AC329" t="n">
+        <v>0.2804605423272933</v>
+      </c>
+      <c r="AD329" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF329" t="n">
+        <v>0.000562938194348721</v>
+      </c>
+      <c r="AG329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI329" t="n">
+        <v>0.0004565494235283376</v>
+      </c>
+      <c r="AJ329" t="n">
+        <v>0.0009656552141006922</v>
+      </c>
+      <c r="AK329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL329" t="n">
+        <v>0.12547802750248</v>
+      </c>
+      <c r="AM329" t="n">
+        <v>0.1644906833750761</v>
+      </c>
+      <c r="AN329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO329" t="n">
+        <v>0.0002142650422300863</v>
+      </c>
+      <c r="AP329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ329" t="n">
+        <v>0.07720890427162015</v>
+      </c>
+      <c r="AR329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS329" t="n">
+        <v>3941</v>
+      </c>
+      <c r="AT329" t="n">
+        <v>3783</v>
+      </c>
+      <c r="AU329" t="n">
+        <v>0.959908652626237</v>
+      </c>
+      <c r="AV329" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ329" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA329" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB329" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC329" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD329" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE329" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF329" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG329" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH329" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI329" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ329" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK329" t="n">
+        <v>0.0005006229841190559</v>
+      </c>
+      <c r="BL329" t="n">
+        <v>0.02035477533730366</v>
+      </c>
+      <c r="BM329" t="n">
+        <v>0.07349122400296981</v>
+      </c>
+      <c r="BN329" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO329" t="n">
+        <v>0.02674511282075128</v>
+      </c>
+      <c r="BP329" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ329" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR329" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS329" t="n">
+        <v>0.0001800304580416954</v>
+      </c>
+      <c r="BT329" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU329" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV329" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW329" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX329" t="n">
+        <v>0.09191423789252953</v>
+      </c>
+      <c r="BY329" t="n">
+        <v>0.2469371555456077</v>
+      </c>
+      <c r="BZ329" t="inlineStr"/>
+      <c r="CA329" t="inlineStr"/>
+      <c r="CB329" t="inlineStr"/>
+      <c r="CC329" t="inlineStr"/>
+      <c r="CD329" t="inlineStr"/>
+      <c r="CE329" t="inlineStr"/>
+      <c r="CF329" t="inlineStr"/>
+      <c r="CG329" t="inlineStr"/>
+      <c r="CH329" t="inlineStr"/>
+      <c r="CI329" t="inlineStr"/>
+      <c r="CJ329" t="inlineStr"/>
+      <c r="CK329" t="inlineStr"/>
+      <c r="CL329" t="inlineStr"/>
+      <c r="CM329" t="inlineStr"/>
+      <c r="CN329" t="inlineStr"/>
+      <c r="CO329" t="inlineStr"/>
+      <c r="CP329" t="inlineStr"/>
+      <c r="CQ329" t="inlineStr"/>
+      <c r="CR329" t="inlineStr"/>
+      <c r="CS329" t="inlineStr"/>
+      <c r="CT329" t="inlineStr"/>
+      <c r="CU329" t="inlineStr"/>
+      <c r="CV329" t="inlineStr"/>
+      <c r="CW329" t="inlineStr"/>
+      <c r="CX329" t="inlineStr"/>
+      <c r="CY329" t="inlineStr"/>
+      <c r="CZ329" t="inlineStr"/>
+      <c r="DA329" t="inlineStr"/>
+      <c r="DB329" t="inlineStr"/>
+      <c r="DC329" t="inlineStr"/>
+      <c r="DD329" t="inlineStr"/>
+      <c r="DE329" t="inlineStr"/>
+      <c r="DF329" t="inlineStr"/>
+      <c r="DG329" t="inlineStr"/>
+      <c r="DH329" t="inlineStr"/>
+      <c r="DI329" t="inlineStr"/>
+      <c r="DJ329" t="inlineStr"/>
+      <c r="DK329" t="inlineStr"/>
+      <c r="DL329" t="inlineStr"/>
+      <c r="DM329" t="inlineStr"/>
+      <c r="DN329" t="inlineStr"/>
+      <c r="DO329" t="inlineStr"/>
+      <c r="DP329" t="inlineStr"/>
+      <c r="DQ329" t="inlineStr"/>
+      <c r="DR329" t="inlineStr"/>
+      <c r="DS329" t="inlineStr"/>
+      <c r="DT329" t="inlineStr"/>
+      <c r="DU329" t="inlineStr"/>
+      <c r="DV329" t="inlineStr"/>
+      <c r="DW329" t="inlineStr"/>
+      <c r="DX329" t="n">
+        <v>1.526860040427512</v>
+      </c>
+      <c r="DY329" t="n">
+        <v>1.991917000642492</v>
+      </c>
+      <c r="DZ329" t="n">
+        <v>1.758530954654171</v>
+      </c>
+      <c r="EA329" t="n">
+        <v>0.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
